--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B228BCA-3D32-8A43-8658-CD78868A068F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DEF36C-3C9C-4558-B6D2-D7E213D7BF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2499,7 +2488,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3874,30 +3863,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3912,7 +3901,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4201,7 +4190,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4210,7 +4199,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4227,7 +4216,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4241,7 +4230,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>420</v>
       </c>
@@ -4250,7 +4239,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>317</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4267,7 +4256,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>309</v>
       </c>
@@ -4277,7 +4266,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4287,17 +4276,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>423</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>422</v>
       </c>
@@ -4307,17 +4296,17 @@
       <c r="D11" s="49"/>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>421</v>
       </c>
@@ -4327,13 +4316,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>425</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23388.966892</v>
+        <v>23344.753344000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4341,7 +4330,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>424</v>
       </c>
@@ -4355,7 +4344,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4365,27 +4354,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="349" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>308</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>351</v>
       </c>
@@ -4400,7 +4389,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4413,7 +4402,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>439</v>
       </c>
@@ -4421,7 +4410,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>440</v>
       </c>
@@ -4429,7 +4418,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>350</v>
       </c>
@@ -4445,28 +4434,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>5.8997320626290684</v>
+        <v>6.9895661568976033</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>403</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>7.371853255114913E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.13284675364661358</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>438</v>
       </c>
@@ -4485,13 +4474,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>430</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>2.4694213056228387</v>
+        <v>3.2714103607293628</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4501,16 +4490,16 @@
         <v>429</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>431</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>3.6595136061107914</v>
+        <v>4.6114224254647684</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4520,16 +4509,16 @@
         <v>442</v>
       </c>
       <c r="F30" s="342">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.187</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>432</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>5.2013940191322048</v>
+        <v>6.4058499272029952</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4539,16 +4528,16 @@
         <v>441</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>433</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>4.6820808344833802</v>
+        <v>5.9535611226219638</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4558,14 +4547,14 @@
         <v>443</v>
       </c>
       <c r="F32" s="342">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>358</v>
       </c>
@@ -4575,25 +4564,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="349" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="352" t="s">
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="349" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4602,16 +4591,16 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="350" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4624,20 +4613,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="350" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4650,7 +4639,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4663,16 +4652,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="350" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4685,16 +4674,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="350" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
@@ -4709,7 +4698,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
@@ -4724,7 +4713,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4737,12 +4726,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4755,16 +4744,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="350" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4777,8 +4766,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="350" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="348" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="351"/>
@@ -4786,7 +4775,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4799,25 +4788,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="349" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="347" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="349" t="s">
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4830,7 +4819,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4843,23 +4832,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>394</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.3478279172297601E-2</v>
+        <v>4.3560624398002713E-2</v>
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>310</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.799621928166351E-2</v>
+        <v>3.8068181818181814E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>453</v>
@@ -4869,7 +4858,7 @@
         <v>0.87391267559349473</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>359</v>
       </c>
@@ -4879,43 +4868,43 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="352" t="s">
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
+    </row>
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>436</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>435</v>
       </c>
@@ -4924,43 +4913,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>360</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="349" t="s">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B83" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
-    </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="349" t="s">
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B84" s="347" t="s">
         <v>368</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
+    </row>
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4968,20 +4957,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.875001210268179</v>
+        <v>3.8333349470242393</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>361</v>
       </c>
@@ -4991,38 +4980,38 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="349" t="s">
+    <row r="91" spans="1:6">
+      <c r="B91" s="347" t="s">
         <v>369</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="349" t="s">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B95" s="347" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
+    </row>
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5035,7 +5024,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5048,7 +5037,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>408</v>
       </c>
@@ -5057,7 +5046,7 @@
         <v>0.70576761251783326</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>409</v>
       </c>
@@ -5066,7 +5055,7 @@
         <v>2.5694600492681609E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>411</v>
       </c>
@@ -5075,12 +5064,12 @@
         <v>0.53421555755411909</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5093,7 +5082,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5106,7 +5095,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5119,12 +5108,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5137,7 +5126,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5150,29 +5139,29 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="349" t="s">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B111" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
+    </row>
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>454</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>5.2697873160646571</v>
+        <v>6.2281210528207165</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>410</v>
       </c>
@@ -5185,7 +5174,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>362</v>
       </c>
@@ -5195,16 +5184,16 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="350" t="s">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B118" s="348" t="s">
         <v>371</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
-    </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5221,7 +5210,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5236,14 +5225,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>7.4 CNY</v>
+        <v>8.85 CNY</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5258,14 +5247,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>6.13 CNY</v>
+        <v>7.26 CNY</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.17</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5280,14 +5269,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>5.77 CNY</v>
+        <v>6.83 CNY</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.51</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5302,14 +5291,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>5.36 CNY</v>
+        <v>6.34 CNY</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.17</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5324,36 +5313,36 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>5.27 CNY</v>
+        <v>6.23 CNY</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>5.8997320626290684</v>
+        <v>6.9895661568976033</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="353" t="s">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B129" s="352" t="s">
         <v>374</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
-    </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>406</v>
       </c>
@@ -5363,30 +5352,30 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="354" t="s">
+    <row r="133" spans="1:6">
+      <c r="B133" s="350" t="s">
         <v>372</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
-    </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="349" t="s">
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="347" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
+    </row>
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5395,16 +5384,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5417,7 +5406,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>413</v>
       </c>
@@ -5430,49 +5419,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>412</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>0.31937317784256547</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.34688091727946951</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>2.1500481277802734</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2.9245294434498934</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>2.4694213056228387</v>
+        <v>3.2714103607293628</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>421</v>
       </c>
@@ -5485,63 +5474,63 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.58143500765653378</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.53195802324569241</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>415</v>
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.187</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>0.4104905256387098</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.43217519804432247</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>3.2490230804720817</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>4.1792472274204462</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>3.6595136061107914</v>
+        <v>4.6114224254647684</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>421</v>
       </c>
@@ -5554,63 +5543,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37971528753120687</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.34024196610342983</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>414</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>0.51799649443682394</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.53727540184178957</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>4.6833975246953807</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>5.8685745253612058</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>405</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>5.2013940191322048</v>
+        <v>6.4058499272029952</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>421</v>
       </c>
@@ -5623,63 +5612,63 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.11836775570205582</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.3512512306442965E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C166" s="238">
         <f>Scenarios!C103</f>
-        <v>0.48276808491253681</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.51152290174831927</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>4.1993127495708436</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>5.4420382208736449</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>405</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>4.6820808344833802</v>
+        <v>5.9535611226219638</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>421</v>
       </c>
@@ -5692,16 +5681,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.20651643662874097</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.14739695926290697</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>378</v>
       </c>
@@ -5711,21 +5700,21 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="348" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="354" t="s">
         <v>380</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
+    </row>
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>384</v>
       </c>
@@ -5734,80 +5723,91 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="350" t="s">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="348" t="s">
         <v>385</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
-    </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
+    </row>
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="347" t="s">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B186" s="353" t="s">
         <v>386</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
-    </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="347" t="s">
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B187" s="353" t="s">
         <v>387</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
-    </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
+    </row>
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5824,17 +5824,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5865,15 +5854,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5922,7 +5911,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5938,7 +5927,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5946,7 +5935,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5982,7 +5971,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6018,7 +6007,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6054,7 +6043,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6090,7 +6079,7 @@
       </c>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6126,7 +6115,7 @@
       </c>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6142,7 +6131,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6158,7 +6147,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6174,7 +6163,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6204,7 +6193,7 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6234,7 +6223,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6270,7 +6259,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6306,7 +6295,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6342,13 +6331,13 @@
       </c>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6378,7 +6367,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6394,7 +6383,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6410,7 +6399,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>375</v>
       </c>
@@ -6446,7 +6435,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>377</v>
       </c>
@@ -6482,7 +6471,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>376</v>
       </c>
@@ -6518,7 +6507,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6541,7 +6530,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6549,7 +6538,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6586,7 +6575,7 @@
       </c>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6623,7 +6612,7 @@
       </c>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6660,7 +6649,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6697,7 +6686,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6734,7 +6723,7 @@
       </c>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6750,12 +6739,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6804,7 +6793,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6853,7 +6842,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6902,7 +6891,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6951,7 +6940,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7000,7 +6989,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7049,7 +7038,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7098,7 +7087,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7147,7 +7136,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7196,7 +7185,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7245,7 +7234,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7294,7 +7283,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7343,7 +7332,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7392,12 +7381,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7446,7 +7435,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7495,12 +7484,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7549,7 +7538,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7598,7 +7587,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7647,7 +7636,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7696,13 +7685,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7751,7 +7740,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7800,7 +7789,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7849,7 +7838,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>397</v>
       </c>
@@ -7898,7 +7887,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7947,12 +7936,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8002,7 +7991,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8051,7 +8040,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8101,7 +8090,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8150,7 +8139,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8200,7 +8189,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8216,13 +8205,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8271,7 +8260,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8305,7 +8294,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8339,7 +8328,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8388,7 +8377,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8469,7 +8458,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8480,7 +8469,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8496,7 +8485,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8507,7 +8496,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8527,7 +8516,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8549,7 +8538,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8570,7 +8559,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8592,7 +8581,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8613,7 +8602,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8634,7 +8623,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8656,7 +8645,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8668,7 +8657,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8680,7 +8669,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8704,12 +8693,12 @@
         <v>1152452.19</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8729,7 +8718,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8749,7 +8738,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8769,7 +8758,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8789,7 +8778,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8809,7 +8798,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8830,7 +8819,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8850,7 +8839,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8870,7 +8859,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8882,7 +8871,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8894,7 +8883,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8918,7 +8907,7 @@
         <v>143297.514</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8935,7 +8924,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8954,7 +8943,7 @@
         <v>41368.748499999987</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8969,7 +8958,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8988,7 +8977,7 @@
         <v>-159497.01150000002</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9004,7 +8993,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -9021,7 +9010,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9041,7 +9030,7 @@
         <v>2036939.2285</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9052,7 +9041,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -9065,7 +9054,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9084,7 +9073,7 @@
         <v>741189.52450000006</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9100,7 +9089,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9116,7 +9105,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9132,7 +9121,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9151,7 +9140,7 @@
         <v>138977.209</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9171,7 +9160,7 @@
         <v>1295749.7039999999</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9191,7 +9180,7 @@
         <v>546033.79799999995</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9210,7 +9199,7 @@
         <v>749715.90599999996</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9221,7 +9210,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9235,7 +9224,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9249,7 +9238,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9264,10 +9253,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9280,7 +9269,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9294,7 +9283,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9305,10 +9294,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9320,7 +9309,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9334,7 +9323,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9348,10 +9337,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9363,7 +9352,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9374,7 +9363,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9385,10 +9374,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9400,7 +9389,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9416,7 +9405,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9427,7 +9416,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9441,7 +9430,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9457,7 +9446,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9467,7 +9456,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9477,7 +9466,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9487,7 +9476,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9497,10 +9486,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>320</v>
       </c>
@@ -9512,7 +9501,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>319</v>
       </c>
@@ -9528,7 +9517,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>324</v>
       </c>
@@ -9544,7 +9533,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>322</v>
       </c>
@@ -9557,7 +9546,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>325</v>
       </c>
@@ -9570,10 +9559,10 @@
         <v>326</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9585,7 +9574,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9599,7 +9588,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9613,7 +9602,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9627,7 +9616,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9641,7 +9630,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>290</v>
       </c>
@@ -9652,7 +9641,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>291</v>
       </c>
@@ -9660,7 +9649,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>288</v>
       </c>
@@ -9677,7 +9666,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>289</v>
       </c>
@@ -9694,7 +9683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9711,7 +9700,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>293</v>
       </c>
@@ -9742,19 +9731,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9811,7 +9800,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9834,7 +9823,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9848,7 +9837,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9905,7 +9894,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9960,7 +9949,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10015,7 +10004,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10070,7 +10059,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10127,7 +10116,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10182,7 +10171,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10237,7 +10226,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10294,7 +10283,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10349,7 +10338,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10404,7 +10393,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10459,7 +10448,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10516,7 +10505,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10573,7 +10562,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10599,7 +10588,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10624,7 +10613,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10681,7 +10670,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10700,7 +10689,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10723,7 +10712,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10744,7 +10733,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10801,7 +10790,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10858,7 +10847,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10915,18 +10904,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10985,7 +10974,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11045,7 +11034,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11100,18 +11089,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11168,7 +11157,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11227,7 +11216,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11284,18 +11273,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11353,7 +11342,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11411,7 +11400,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11466,18 +11455,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11535,10 +11524,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11561,14 +11550,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11623,7 +11612,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>348</v>
@@ -11678,7 +11667,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>345</v>
@@ -11735,7 +11724,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11790,11 +11779,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11804,7 +11793,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11831,7 +11820,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11858,7 +11847,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11913,11 +11902,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11927,7 +11916,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11982,7 +11971,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -12037,7 +12026,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12092,7 +12081,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12147,7 +12136,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12203,7 +12192,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12258,11 +12247,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12272,7 +12261,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12297,7 +12286,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12322,7 +12311,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12347,7 +12336,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12374,10 +12363,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12400,7 +12389,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12421,7 +12410,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12478,7 +12467,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12535,7 +12524,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12592,7 +12581,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12649,7 +12638,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12706,7 +12695,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12765,7 +12754,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12822,7 +12811,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12879,7 +12868,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12936,7 +12925,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12993,7 +12982,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13051,7 +13040,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13108,7 +13097,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13134,7 +13123,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13158,7 +13147,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13215,18 +13204,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13282,7 +13271,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13338,7 +13327,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13393,23 +13382,23 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>311</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.799621928166351E-2</v>
+        <v>3.8068181818181814E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.799621928166351E-2</v>
+        <v>3.8068181818181814E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7788279773156899E-2</v>
+        <v>2.784090909090909E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -13448,11 +13437,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13473,7 +13462,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13530,7 +13519,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13587,10 +13576,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13613,7 +13602,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13623,7 +13612,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13680,7 +13669,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13737,7 +13726,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13794,7 +13783,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13851,7 +13840,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13908,11 +13897,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13935,7 +13924,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13992,7 +13981,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -14049,7 +14038,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14076,18 +14065,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>395</v>
@@ -14139,7 +14128,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>396</v>
@@ -14191,11 +14180,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14249,7 +14238,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14304,7 +14293,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14358,7 +14347,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14414,7 +14403,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14471,7 +14460,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14490,7 +14479,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14513,7 +14502,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14534,7 +14523,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14592,795 +14581,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3478279172297601E-2</v>
+        <v>4.3560624398002713E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.1046068163247383E-2</v>
+        <v>6.1161685716586867E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.7872717362159633E-2</v>
+        <v>5.798232478140615E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.2748522776091409E-2</v>
+        <v>3.2810546493470372E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.5958096842905488E-2</v>
+        <v>2.6007259905107959E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.1962507162793908E-2</v>
+        <v>1.1985163426359805E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6683748955291698E-2</v>
+        <v>1.6715346964676719E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.4745863756848938E-3</v>
+        <v>-3.4811670316994485E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.3224275303318092E-2</v>
+        <v>4.3306139461089521E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3141524655590131E-2</v>
+        <v>2.3185353300771174E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12517748614204158</v>
+        <v>0.12541456471428028</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>398</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3475411295220703E-2</v>
+        <v>9.3652448059037413E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9705455889872731E-2</v>
+        <v>6.9837473798755073E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.198177998600931E-2</v>
+        <v>6.20991697208313E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5904631517830618E-2</v>
+        <v>1.5934753926008325E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.562836343682315E-2</v>
+        <v>1.5657962609998952E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2247763713667153E-3</v>
+        <v>1.2270960235852128E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4135271715360896E-3</v>
+        <v>3.4199921851185439E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.093432195021297E-2</v>
+        <v>2.0973970287239886E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6133791332573582E-2</v>
+        <v>5.6240105331309513E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14580676909532306</v>
+        <v>0.14608291827921571</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15402,16 +15391,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15423,7 +15412,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15436,7 +15425,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15457,24 +15446,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1271140.0401025023</v>
+        <v>1694853.3868033364</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15486,7 +15475,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15502,7 +15491,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15518,7 +15507,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15534,13 +15523,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>2329959.9444861589</v>
+        <v>2753673.291186993</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15548,7 +15537,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15562,13 +15551,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.2697873160646571</v>
+        <v>6.2281210528207165</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15576,10 +15565,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15589,13 +15578,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15605,7 +15594,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15615,13 +15604,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>5.9006651815076161</v>
+        <v>6.9828054066931156</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15629,10 +15618,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15650,7 +15639,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15664,15 +15653,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.94339622641509424</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>99935.219927610829</v>
+        <v>101820.79011492425</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15686,15 +15675,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.88999644001423983</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>98209.558613764253</v>
+        <v>101950.54215654559</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15708,15 +15697,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.8396192830323016</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>96513.695673026406</v>
+        <v>102080.45954349852</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15730,15 +15719,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.79209366323802044</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>94847.116553073036</v>
+        <v>102210.54248648556</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15752,15 +15741,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.74725817286605689</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>93209.315586766097</v>
+        <v>102340.79119647763</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15774,15 +15763,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.70496054043967626</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>91599.79583872619</v>
+        <v>102471.20588471467</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15796,15 +15785,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.66505711362233599</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>90018.068954554285</v>
+        <v>102601.78676270564</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15818,15 +15807,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.62741237134182648</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>88463.655012657007</v>
+        <v>102732.53404222913</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15840,15 +15829,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.59189846353002495</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>86936.082378630759</v>
+        <v>102863.44793533355</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15862,15 +15851,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>85434.887562160118</v>
+        <v>102994.52865433756</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15892,7 +15881,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15914,7 +15903,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15936,7 +15925,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15958,7 +15947,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15980,7 +15969,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -16002,7 +15991,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -16024,7 +16013,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -16046,7 +16035,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -16068,7 +16057,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -16090,7 +16079,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16112,7 +16101,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16134,7 +16123,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16156,7 +16145,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16178,7 +16167,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16200,7 +16189,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16222,7 +16211,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16244,7 +16233,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16266,7 +16255,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16288,7 +16277,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16310,13 +16299,13 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1349125.4690227464</v>
+        <v>1798833.9586969954</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16324,30 +16313,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>624906.13186053152</v>
+        <v>1004459.4870739471</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>1550073.5279615005</v>
+        <v>2028526.1158511993</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16357,10 +16346,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>1550073.5279615005</v>
+        <v>2028526.1158511993</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16384,141 +16373,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1271140.0401025021</v>
+        <v>1694853.386803336</v>
       </c>
       <c r="C56" s="124">
-        <v>1291496.6179442196</v>
+        <v>1720030.814793431</v>
       </c>
       <c r="D56" s="124">
-        <v>1375994.0377045462</v>
+        <v>1824063.1825040856</v>
       </c>
       <c r="E56" s="124">
-        <v>1442781.8926012209</v>
+        <v>1905783.395825529</v>
       </c>
       <c r="F56" s="124">
-        <v>1489039.0096932889</v>
+        <v>1962138.7895844979</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>1271140.0401025019</v>
+        <v>1694853.3868033355</v>
       </c>
       <c r="C57" s="124">
-        <v>1311201.9172695512</v>
+        <v>1742984.9715916547</v>
       </c>
       <c r="D57" s="124">
-        <v>1492028.1900095176</v>
+        <v>1959330.3932692662</v>
       </c>
       <c r="E57" s="124">
-        <v>1652798.5242227199</v>
+        <v>2150754.4939556615</v>
       </c>
       <c r="F57" s="124">
-        <v>1774121.4504196071</v>
+        <v>2294801.7487464733</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>1271140.0401025016</v>
+        <v>1694853.386803335</v>
       </c>
       <c r="C58" s="124">
-        <v>1334986.3761435125</v>
+        <v>1773335.93203612</v>
       </c>
       <c r="D58" s="124">
-        <v>1647374.8296207064</v>
+        <v>2157725.5203181584</v>
       </c>
       <c r="E58" s="124">
-        <v>1958141.7098947109</v>
+        <v>2540966.1638217429</v>
       </c>
       <c r="F58" s="124">
-        <v>2212895.0903457161</v>
+        <v>2855784.043374842</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>1271140.0401025014</v>
+        <v>1694853.3868033355</v>
       </c>
       <c r="C59" s="124">
-        <v>1358593.7436619736</v>
+        <v>1806381.5450048302</v>
       </c>
       <c r="D59" s="124">
-        <v>1819442.3202743754</v>
+        <v>2398788.937638829</v>
       </c>
       <c r="E59" s="124">
-        <v>2328362.5464845966</v>
+        <v>3060004.4790359829</v>
       </c>
       <c r="F59" s="124">
-        <v>2779785.5643379521</v>
+        <v>3650942.2694116104</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>1271140.0401025014</v>
+        <v>1694853.3868033353</v>
       </c>
       <c r="C60" s="124">
-        <v>1379968.0917959348</v>
+        <v>1839216.0489163534</v>
       </c>
       <c r="D60" s="124">
-        <v>1994173.5576659078</v>
+        <v>2667440.5303773354</v>
       </c>
       <c r="E60" s="124">
-        <v>2742738.0221522232</v>
+        <v>3697592.1928683338</v>
       </c>
       <c r="F60" s="124">
-        <v>3459647.0626301635</v>
+        <v>4697585.6601613443</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>1271140.0401025014</v>
+        <v>1694853.386803335</v>
       </c>
       <c r="C61" s="124">
-        <v>1398311.617976405</v>
+        <v>1870145.566212385</v>
       </c>
       <c r="D61" s="124">
-        <v>2163146.6817266569</v>
+        <v>2952610.4159092563</v>
       </c>
       <c r="E61" s="124">
-        <v>3187164.4032472498</v>
+        <v>4448232.5208333777</v>
       </c>
       <c r="F61" s="124">
-        <v>4244648.3980896687</v>
+        <v>6024212.9296894623</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16528,7 +16517,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16551,193 +16540,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>5.2697873160646571</v>
+        <v>6.2281210528207165</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>5.2697873160646571</v>
+        <v>6.2281210528207165</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>5.2697873160646571</v>
+        <v>6.2281210528207165</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>5.2697873160646571</v>
+        <v>6.2281210528207165</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>5.2697873160646571</v>
+        <v>6.2281210528207165</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.2697873160646562</v>
+        <v>6.2281210528207165</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>5.3158288095944615</v>
+        <v>6.2850661050252912</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>5.5069408636651431</v>
+        <v>6.520361331073774</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>5.6579983062767942</v>
+        <v>6.7051920379906749</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>5.7626203490318062</v>
+        <v>6.8326538597810664</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>5.2697873160646562</v>
+        <v>6.2281210528207147</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>5.3603972738247734</v>
+        <v>6.3369826732188761</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>5.7693811281401217</v>
+        <v>6.8263019689189441</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>6.1330034599493723</v>
+        <v>7.259255462464397</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>6.407405609708734</v>
+        <v>7.585054366435668</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>5.2697873160646553</v>
+        <v>6.2281210528207138</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>5.4141917778848434</v>
+        <v>6.4056289633661088</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>6.1207364177250891</v>
+        <v>7.2750221825713135</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>6.8236134640865451</v>
+        <v>8.141816775720871</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>7.3998019673276909</v>
+        <v>8.8538561704174903</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>5.2697873160646553</v>
+        <v>6.2281210528207147</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>5.4675857455403269</v>
+        <v>6.4803698843361017</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>6.5099100951093813</v>
+        <v>7.8202474092838816</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>7.6609605066488964</v>
+        <v>9.3157517768527409</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>8.6819665970295095</v>
+        <v>10.652305428633023</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>5.2697873160646553</v>
+        <v>6.2281210528207138</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>5.5159291812084188</v>
+        <v>6.5546333293587073</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>6.9051085021486269</v>
+        <v>8.4278701966216136</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>8.5981743119459217</v>
+        <v>10.757815901252689</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>10.219643460899858</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>13.019551302566807</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>5.2697873160646553</v>
+        <v>6.2281210528207138</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>5.5574176547877618</v>
+        <v>6.6245881705671783</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>7.2872834953447159</v>
+        <v>9.0728532356030627</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>9.6033557579023192</v>
+        <v>12.455576795639731</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>11.995120370057895</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>16.020050763791041</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16754,7 +16743,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16769,14 +16758,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>7.3998019673276909</v>
+        <v>8.8538561704174903</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16791,7 +16780,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>6.1330034599493723</v>
+        <v>7.259255462464397</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16799,7 +16788,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16814,7 +16803,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>5.7693811281401217</v>
+        <v>6.8263019689189441</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16822,7 +16811,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16837,7 +16826,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>5.3603972738247734</v>
+        <v>6.3369826732188761</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16845,7 +16834,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16860,21 +16849,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>5.2697873160646553</v>
+        <v>6.2281210528207138</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>312</v>
       </c>
@@ -16882,23 +16871,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16932,16 +16921,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>448</v>
       </c>
@@ -16953,7 +16942,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>447</v>
       </c>
@@ -16966,7 +16955,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>445</v>
       </c>
@@ -16987,24 +16976,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>446</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1110865.3935</v>
+        <v>1481153.858</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17014,13 +17003,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>449</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>2.5125000000000002</v>
+        <v>3.35</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17028,10 +17017,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -17041,13 +17030,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -17057,7 +17046,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -17067,13 +17056,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>3.0638321633619698</v>
+        <v>4.0095282229211753</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17081,10 +17070,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17102,7 +17091,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17116,15 +17105,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.94339622641509424</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>87334.65543296274</v>
+        <v>88982.479120377131</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17138,15 +17127,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.88999644001423983</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>85826.578137010889</v>
+        <v>89095.87107423415</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17160,15 +17149,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.8396192830323016</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>84344.542017030821</v>
+        <v>89209.407525472299</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17182,15 +17171,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.79209366323802044</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>82888.09739922412</v>
+        <v>89323.088658227178</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17204,15 +17193,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.74725817286605689</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>81456.802374669205</v>
+        <v>89436.914656868961</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17226,15 +17215,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.70496054043967626</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>80050.222665239096</v>
+        <v>89550.885706002882</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17248,15 +17237,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.66505711362233599</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>78667.931491834242</v>
+        <v>89665.001990469304</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17270,15 +17259,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.62741237134182648</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>77309.509444890966</v>
+        <v>89779.263695344256</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17292,15 +17281,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.59189846353002495</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>75974.544357125691</v>
+        <v>89893.671005939497</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17314,15 +17303,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>74662.631178476731</v>
+        <v>90008.224107803006</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17344,7 +17333,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17366,7 +17355,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17388,7 +17377,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17410,7 +17399,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17432,7 +17421,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17454,7 +17443,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17476,7 +17465,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17498,7 +17487,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17520,7 +17509,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17542,7 +17531,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17564,7 +17553,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17586,7 +17575,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17608,7 +17597,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17630,7 +17619,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17652,7 +17641,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17674,7 +17663,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17696,7 +17685,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17718,7 +17707,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17740,7 +17729,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17762,13 +17751,13 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>1179017.848344997</v>
+        <v>1572023.7977933295</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17776,30 +17765,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>546113.38968901848</v>
+        <v>877809.87787406251</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>1354628.904187483</v>
+        <v>1772754.6854148009</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17809,10 +17798,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>1354628.904187483</v>
+        <v>1772754.6854148009</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17836,141 +17825,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>1110865.3934999998</v>
+        <v>1481153.8579999995</v>
       </c>
       <c r="C51" s="124">
-        <v>1128655.2649075827</v>
+        <v>1503156.7314593862</v>
       </c>
       <c r="D51" s="124">
-        <v>1202498.6310910764</v>
+        <v>1594071.9362737308</v>
       </c>
       <c r="E51" s="124">
-        <v>1260865.3840609794</v>
+        <v>1665488.2665475446</v>
       </c>
       <c r="F51" s="124">
-        <v>1301290.0650241496</v>
+        <v>1714737.9594915695</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>1110865.3934999998</v>
+        <v>1481153.8579999993</v>
       </c>
       <c r="C52" s="124">
-        <v>1145875.9757643535</v>
+        <v>1523216.6600429146</v>
       </c>
       <c r="D52" s="124">
-        <v>1303902.3475921368</v>
+        <v>1712283.6663535989</v>
       </c>
       <c r="E52" s="124">
-        <v>1444401.5805204567</v>
+        <v>1879571.6143575252</v>
       </c>
       <c r="F52" s="124">
-        <v>1550427.2235640101</v>
+        <v>2005456.3362036608</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>1110865.3934999995</v>
+        <v>1481153.8579999991</v>
       </c>
       <c r="C53" s="124">
-        <v>1166661.5158564406</v>
+        <v>1549740.7490917698</v>
       </c>
       <c r="D53" s="124">
-        <v>1439661.7450592087</v>
+        <v>1885663.6826576078</v>
       </c>
       <c r="E53" s="124">
-        <v>1711244.8608853081</v>
+        <v>2220582.538817998</v>
       </c>
       <c r="F53" s="124">
-        <v>1933877.0692117331</v>
+        <v>2495705.8742629169</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>1110865.3934999995</v>
+        <v>1481153.8579999991</v>
       </c>
       <c r="C54" s="124">
-        <v>1187292.2935682179</v>
+        <v>1578619.7291378824</v>
       </c>
       <c r="D54" s="124">
-        <v>1590033.7061990155</v>
+        <v>2096332.0586760258</v>
       </c>
       <c r="E54" s="124">
-        <v>2034785.5427500375</v>
+        <v>2674176.7016024138</v>
       </c>
       <c r="F54" s="124">
-        <v>2429289.8401067527</v>
+        <v>3190604.7270988859</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>1110865.3934999995</v>
+        <v>1481153.8579999986</v>
       </c>
       <c r="C55" s="124">
-        <v>1205971.6073350348</v>
+        <v>1607314.2183029864</v>
       </c>
       <c r="D55" s="124">
-        <v>1742733.5493776118</v>
+        <v>2331110.0908885882</v>
       </c>
       <c r="E55" s="124">
-        <v>2396913.5233910605</v>
+        <v>3231372.6865231837</v>
       </c>
       <c r="F55" s="124">
-        <v>3023429.4211123013</v>
+        <v>4105279.6531012338</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>1110865.3934999998</v>
+        <v>1481153.8579999988</v>
       </c>
       <c r="C56" s="124">
-        <v>1222002.2473792292</v>
+        <v>1634343.9155179767</v>
       </c>
       <c r="D56" s="124">
-        <v>1890401.3043289324</v>
+        <v>2580323.6685524788</v>
       </c>
       <c r="E56" s="124">
-        <v>2785303.3711981499</v>
+        <v>3887366.7839434934</v>
       </c>
       <c r="F56" s="124">
-        <v>3709452.0385281849</v>
+        <v>5264636.039729842</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17980,7 +17969,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -18003,193 +17992,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>2.5125000000000002</v>
+        <v>3.35</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>2.5125000000000002</v>
+        <v>3.35</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>2.5125000000000002</v>
+        <v>3.35</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>2.5125000000000002</v>
+        <v>3.35</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>2.5125000000000002</v>
+        <v>3.35</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.5124999999999997</v>
+        <v>3.3499999999999992</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>2.552736244798953</v>
+        <v>3.3997650029339113</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>2.7197514913100309</v>
+        <v>3.6053924834843176</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>2.8517625051510893</v>
+        <v>3.7669183810979039</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>2.9431930344611783</v>
+        <v>3.878308882814764</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>2.5124999999999997</v>
+        <v>3.3499999999999983</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>2.5916851906215568</v>
+        <v>3.4451355499515999</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>2.9491013650208231</v>
+        <v>3.8727578848763708</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>3.2668755299177903</v>
+        <v>4.2511214308282277</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>3.5066790468026001</v>
+        <v>4.5358412227031879</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>2.5124999999999988</v>
+        <v>3.3499999999999979</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>2.6386968895969187</v>
+        <v>3.5051264130437345</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>3.2561552062259485</v>
+        <v>4.2649001673821969</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>3.8704083664249431</v>
+        <v>5.0224029494715019</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>4.3739468029386224</v>
+        <v>5.6446632020187941</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>2.5124999999999988</v>
+        <v>3.3499999999999979</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>2.6853585547312737</v>
+        <v>3.5704434512649432</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>3.596259015899415</v>
+        <v>4.7413794040596464</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>4.6021765607909089</v>
+        <v>6.0483196272835054</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>5.4944467250326818</v>
+        <v>7.2163508051850664</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>2.5124999999999988</v>
+        <v>3.349999999999997</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>2.7276064959433581</v>
+        <v>3.6353432172034381</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>3.94162791318537</v>
+        <v>5.2723886598935428</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>5.4212195849811931</v>
+        <v>7.3085577446152561</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>6.8382420273358324</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>9.2851169806622025</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>2.5124999999999997</v>
+        <v>3.3499999999999974</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>2.7638637988953731</v>
+        <v>3.6964776396546521</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>4.2756154840342884</v>
+        <v>5.8360475132022396</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>6.2996603918738883</v>
+        <v>8.7922525103470388</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>8.3898538034726027</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>11.90729149293751</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18206,7 +18195,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18221,14 +18210,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>4.3739468029386224</v>
+        <v>5.6446632020187941</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18243,7 +18232,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>3.2668755299177903</v>
+        <v>4.2511214308282277</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18251,7 +18240,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18266,7 +18255,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>2.9491013650208231</v>
+        <v>3.8727578848763708</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18274,7 +18263,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18289,7 +18278,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>2.5916851906215568</v>
+        <v>3.4451355499515999</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18297,7 +18286,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18312,21 +18301,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>2.5124999999999988</v>
+        <v>3.3499999999999979</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>312</v>
       </c>
@@ -18334,23 +18323,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18380,7 +18369,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18390,7 +18379,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18403,7 +18392,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18412,10 +18401,10 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-5.29</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-5.28</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18435,7 +18424,7 @@
         <v>0.20099999999999998</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18444,7 +18433,7 @@
         <v>0.20099999999999998</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18461,10 +18450,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>6.100732062629068</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>7.1905661568976029</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18489,7 +18478,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18511,7 +18500,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18533,7 +18522,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18544,7 +18533,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>452</v>
       </c>
@@ -18558,7 +18547,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18577,7 +18566,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18595,7 +18584,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18606,7 +18595,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18615,7 +18604,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18623,7 +18612,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18635,24 +18624,24 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>305</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18661,13 +18650,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>5.2697873160646571</v>
+        <v>6.2281210528207165</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18676,7 +18665,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18685,7 +18674,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18697,7 +18686,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18708,13 +18697,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>5.7693811281401217</v>
+        <v>6.8263019689189441</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18723,7 +18712,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18734,7 +18723,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18743,7 +18732,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18755,7 +18744,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18766,13 +18755,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>5.3603972738247734</v>
+        <v>6.3369826732188761</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18781,7 +18770,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18792,7 +18781,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18801,7 +18790,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18813,7 +18802,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18824,13 +18813,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>6.1330034599493723</v>
+        <v>7.259255462464397</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18839,7 +18828,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18851,20 +18840,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>5.7603088236389022</v>
+        <v>6.8150288084880213</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18873,12 +18862,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18888,12 +18877,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18902,7 +18891,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18914,7 +18903,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18925,13 +18914,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>5.2697873160646553</v>
+        <v>6.2281210528207138</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18940,7 +18929,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18951,7 +18940,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>318</v>
       </c>
@@ -18960,7 +18949,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18972,7 +18961,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18983,13 +18972,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>7.3998019673276909</v>
+        <v>8.8538561704174903</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18998,7 +18987,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -19009,13 +18998,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>5.8997320626290684</v>
+        <v>6.9895661568976033</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19029,7 +19018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>352</v>
       </c>
@@ -19038,7 +19027,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>306</v>
       </c>
@@ -19046,7 +19035,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -19059,7 +19048,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -19071,13 +19060,13 @@
         <v>314</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>5.9006651815076161</v>
+        <v>6.9828054066931156</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19087,7 +19076,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>353</v>
       </c>
@@ -19095,7 +19084,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>307</v>
       </c>
@@ -19105,7 +19094,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>295</v>
       </c>
@@ -19117,7 +19106,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>294</v>
       </c>
@@ -19127,7 +19116,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>286</v>
       </c>
@@ -19140,10 +19129,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>0.40591438397107493</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.34262299719893202</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19152,12 +19141,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>299</v>
       </c>
@@ -19167,7 +19156,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19180,49 +19169,49 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>301</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.31937317784256547</v>
+        <v>0.34688091727946951</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>2.1500481277802734</v>
+        <v>2.9245294434498934</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>2.4694213056228387</v>
+        <v>3.2714103607293628</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19233,85 +19222,85 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.58143500765653378</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.53195802324569241</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>302</v>
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>300</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>7.371853255114913E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.13284675364661358</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>418</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.187</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.4104905256387098</v>
+        <v>0.43217519804432247</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>3.2490230804720817</v>
+        <v>4.1792472274204462</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>3.6595136061107914</v>
+        <v>4.6114224254647684</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19322,58 +19311,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.37971528753120687</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.34024196610342983</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>401</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>407</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.51799649443682394</v>
+        <v>0.53727540184178957</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>4.6833975246953807</v>
+        <v>5.8685745253612058</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>402</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>5.2013940191322048</v>
+        <v>6.4058499272029952</v>
       </c>
       <c r="D99" t="s">
         <v>400</v>
@@ -19383,53 +19372,53 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>0.11836775570205582</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>8.3512512306442965E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>426</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.48276808491253681</v>
+        <v>0.51152290174831927</v>
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>4.1993127495708436</v>
+        <v>5.4420382208736449</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>402</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>4.6820808344833802</v>
+        <v>5.9535611226219638</v>
       </c>
       <c r="D105" t="s">
         <v>400</v>
@@ -19439,19 +19428,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.20651643662874097</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.14739695926290697</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>327</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>328</v>
       </c>
@@ -19459,7 +19448,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>328</v>
       </c>
@@ -19467,7 +19456,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>328</v>
       </c>

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568F7C71-4CBA-4C69-8A6B-65EE2E49A26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBEB411-F3CA-4582-A1BA-466990E1D3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3868,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4308,7 +4308,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23344.753344000001</v>
+        <v>23212.112700000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4366,13 +4366,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13284675364661358</v>
+        <v>0.13507251173285395</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4497,7 +4497,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="305">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4572,22 +4572,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4599,13 +4599,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4625,13 +4625,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4660,13 +4660,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4752,13 +4752,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4796,22 +4796,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.3560624398002713E-2</v>
+        <v>4.3809542251705587E-2</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8068181818181814E-2</v>
+        <v>3.8285714285714284E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4880,22 +4880,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4939,22 +4939,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4991,13 +4991,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5010,13 +5010,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5147,13 +5147,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5192,13 +5192,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5341,13 +5341,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5360,22 +5360,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C137" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C141" s="299">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="C142" s="216">
         <f>Scenarios!C81</f>
-        <v>0.34688091727946946</v>
+        <v>0.34688091727946951</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5708,13 +5708,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5751,13 +5751,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5765,22 +5765,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5804,6 +5804,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5820,17 +5831,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13396,16 +13396,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8068181818181814E-2</v>
+        <v>3.8285714285714284E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8068181818181814E-2</v>
+        <v>3.8285714285714284E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.784090909090909E-2</v>
+        <v>2.7999999999999997E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14595,50 +14595,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3560624398002713E-2</v>
+        <v>4.3809542251705587E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.1161685716586867E-2</v>
+        <v>6.1511181063538797E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.798232478140615E-2</v>
+        <v>5.8313652351585615E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.2810546493470372E-2</v>
+        <v>3.2998035330575916E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.6007259905107959E-2</v>
+        <v>2.6155872818851435E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.1985163426359805E-2</v>
+        <v>1.2053650074510433E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6715346964676719E-2</v>
+        <v>1.6810863233046303E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.4811670316994485E-3</v>
+        <v>-3.5010594147377311E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.3306139461089521E-2</v>
+        <v>4.3553603115152897E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3185353300771174E-2</v>
+        <v>2.3317841033918436E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12541456471428028</v>
+        <v>0.12613121936979046</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14652,43 +14652,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3652448059037413E-2</v>
+        <v>9.4187604905089053E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9837473798755073E-2</v>
+        <v>7.02365450776051E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.20991697208313E-2</v>
+        <v>6.245402211923605E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5934753926008325E-2</v>
+        <v>1.6025809662728374E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5657962609998952E-2</v>
+        <v>1.5747436682056089E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2270960235852128E-3</v>
+        <v>1.2341080008628426E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4199921851185439E-3</v>
+        <v>3.4395349976049359E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0973970287239886E-2</v>
+        <v>2.1093821546024114E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6240105331309513E-2</v>
+        <v>5.6561477361774137E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14608291827921571</v>
+        <v>0.14691767781223983</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.28</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.34688091727946946</v>
+        <v>0.34688091727946951</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13284675364661358</v>
+        <v>0.13507251173285395</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D798D085-08BE-4753-851F-3BD36C43BC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F0F19A-DDBD-4FD0-8AFA-2073855FB4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4380,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4586,22 +4586,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,13 +4613,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4639,13 +4639,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4674,13 +4674,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4696,13 +4696,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4766,13 +4766,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4788,7 +4788,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4810,22 +4810,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4960,22 +4960,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5019,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5071,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5218,13 +5218,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5263,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5412,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5431,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5779,13 +5779,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5822,13 +5822,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5836,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5875,6 +5875,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5891,17 +5902,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F0F19A-DDBD-4FD0-8AFA-2073855FB4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DD07F7-1AC6-4156-9FEC-2E8461A2FF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4322,7 +4322,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>5.25</v>
+        <v>5.18</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23212.112700000001</v>
+        <v>22902.617864</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4380,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="350" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="350"/>
+      <c r="D18" s="350"/>
+      <c r="E18" s="350"/>
+      <c r="F18" s="350"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13507251173285395</v>
+        <v>0.14033403532037614</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4511,7 +4511,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4586,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="350" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="350"/>
+      <c r="D36" s="350"/>
+      <c r="E36" s="350"/>
+      <c r="F36" s="350"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="353" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="353"/>
+      <c r="D37" s="353"/>
+      <c r="E37" s="353"/>
+      <c r="F37" s="353"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,13 +4613,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="351" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="351"/>
+      <c r="D40" s="351"/>
+      <c r="E40" s="351"/>
+      <c r="F40" s="351"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4639,13 +4639,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="351" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="351"/>
+      <c r="D43" s="351"/>
+      <c r="E43" s="351"/>
+      <c r="F43" s="351"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4674,13 +4674,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="351" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="351"/>
+      <c r="D47" s="351"/>
+      <c r="E47" s="351"/>
+      <c r="F47" s="351"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4696,13 +4696,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="351" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="351"/>
+      <c r="D50" s="351"/>
+      <c r="E50" s="351"/>
+      <c r="F50" s="351"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4766,13 +4766,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="351" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="351"/>
+      <c r="D58" s="351"/>
+      <c r="E58" s="351"/>
+      <c r="F58" s="351"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4788,7 +4788,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="351" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4810,22 +4810,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="350" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="350"/>
+      <c r="D64" s="350"/>
+      <c r="E64" s="350"/>
+      <c r="F64" s="350"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="350" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="350"/>
+      <c r="D65" s="350"/>
+      <c r="E65" s="350"/>
+      <c r="F65" s="350"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.3809542251705587E-2</v>
+        <v>4.4401563092944851E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8285714285714284E-2</v>
+        <v>3.8803088803088803E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4960,22 +4960,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="350" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="350"/>
+      <c r="D80" s="350"/>
+      <c r="E80" s="350"/>
+      <c r="F80" s="350"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="353" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="353"/>
+      <c r="D81" s="353"/>
+      <c r="E81" s="353"/>
+      <c r="F81" s="353"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5019,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="350" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="350"/>
+      <c r="D89" s="350"/>
+      <c r="E89" s="350"/>
+      <c r="F89" s="350"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="350" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="350"/>
+      <c r="D90" s="350"/>
+      <c r="E90" s="350"/>
+      <c r="F90" s="350"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5071,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="350" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="350"/>
+      <c r="D97" s="350"/>
+      <c r="E97" s="350"/>
+      <c r="F97" s="350"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="350" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="350"/>
+      <c r="D101" s="350"/>
+      <c r="E101" s="350"/>
+      <c r="F101" s="350"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5218,13 +5218,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="350" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="350"/>
+      <c r="D116" s="350"/>
+      <c r="E116" s="350"/>
+      <c r="F116" s="350"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5263,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="351" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="351"/>
+      <c r="D123" s="351"/>
+      <c r="E123" s="351"/>
+      <c r="F123" s="351"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5412,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="354" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="354"/>
+      <c r="D134" s="354"/>
+      <c r="E134" s="354"/>
+      <c r="F134" s="354"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5431,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="355" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="355"/>
+      <c r="D138" s="355"/>
+      <c r="E138" s="355"/>
+      <c r="F138" s="355"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="350" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="350"/>
+      <c r="D139" s="350"/>
+      <c r="E139" s="350"/>
+      <c r="F139" s="350"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.34688091727946946</v>
+        <v>0.34688091727946951</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5779,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="349" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="350"/>
+      <c r="D179" s="350"/>
+      <c r="E179" s="350"/>
+      <c r="F179" s="350"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5822,13 +5822,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="351" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="351"/>
+      <c r="D188" s="351"/>
+      <c r="E188" s="351"/>
+      <c r="F188" s="351"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5836,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="348" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="348"/>
+      <c r="D191" s="348"/>
+      <c r="E191" s="348"/>
+      <c r="F191" s="348"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="348" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="348"/>
+      <c r="D192" s="348"/>
+      <c r="E192" s="348"/>
+      <c r="F192" s="348"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5875,17 +5875,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,6 +5891,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,16 +13467,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8285714285714284E-2</v>
+        <v>3.8803088803088803E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8285714285714284E-2</v>
+        <v>3.8803088803088803E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7999999999999997E-2</v>
+        <v>2.837837837837838E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3809542251705587E-2</v>
+        <v>4.4401563092944851E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.1511181063538797E-2</v>
+        <v>6.2342413240073107E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.8313652351585615E-2</v>
+        <v>5.9101674680661097E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.2998035330575916E-2</v>
+        <v>3.3443954726935052E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.6155872818851435E-2</v>
+        <v>2.6509330559646726E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.2053650074510433E-2</v>
+        <v>1.2216537237679494E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6810863233046303E-2</v>
+        <v>1.7038037060519904E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.5010594147377311E-3</v>
+        <v>-3.5483710284504033E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.3553603115152897E-2</v>
+        <v>4.4142165319411716E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3317841033918436E-2</v>
+        <v>2.3632946993836255E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12613121936979046</v>
+        <v>0.12783569530722005</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4187604905089053E-2</v>
+        <v>9.546041037677945E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.02365450776051E-2</v>
+        <v>7.1185687578653817E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.245402211923605E-2</v>
+        <v>6.329799539111762E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6025809662728374E-2</v>
+        <v>1.624237465817065E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5747436682056089E-2</v>
+        <v>1.5960239880462253E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2341080008628426E-3</v>
+        <v>1.2507851360096377E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4395349976049359E-3</v>
+        <v>3.4860152002752728E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1093821546024114E-2</v>
+        <v>2.1378873188537956E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6561477361774137E-2</v>
+        <v>5.7325821650446765E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14691767781223983</v>
+        <v>0.14890305183672953</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.25</v>
+        <v>-5.18</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18719,7 +18719,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.25</v>
+        <v>5.18</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19258,7 +19258,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19267,7 +19267,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.34688091727946946</v>
+        <v>0.34688091727946951</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.25</v>
+        <v>5.18</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13507251173285395</v>
+        <v>0.14033403532037614</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DD07F7-1AC6-4156-9FEC-2E8461A2FF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98902AC0-E7A4-4680-B1BD-4F6822C814A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2501,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3149,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3821,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3865,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3882,29 +3856,71 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4380,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4511,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,19 +4629,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>135997.4245838768</v>
       </c>
@@ -4639,19 +4655,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>154945.9</v>
       </c>
@@ -4664,7 +4680,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-154945.9</v>
       </c>
@@ -4674,19 +4690,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4696,19 +4712,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>4618.7267156970447</v>
       </c>
@@ -4723,7 +4739,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-1984.19</v>
       </c>
@@ -4738,7 +4754,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>2634.5367156970447</v>
       </c>
@@ -4756,7 +4772,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-2282.7677664801586</v>
       </c>
@@ -4766,19 +4782,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-34657.990324893457</v>
       </c>
@@ -4788,19 +4804,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4810,28 +4826,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>142780.44671569683</v>
       </c>
@@ -4844,7 +4860,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>101691.20320820018</v>
       </c>
@@ -4883,10 +4899,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4908,11 +4924,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>5.0475725130946753E-2</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>6.490075699179193E-2</v>
       </c>
@@ -4922,11 +4938,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.56944999111533989</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.62106298336522048</v>
       </c>
@@ -4936,11 +4952,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.7057676125178334</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.7057676125178334</v>
       </c>
@@ -4960,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,19 +5106,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>72651.94</v>
       </c>
@@ -5128,7 +5144,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>2.5694600492681609E-2</v>
       </c>
@@ -5137,7 +5153,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>0.53421555755411909</v>
       </c>
@@ -5151,7 +5167,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>606704.22</v>
       </c>
@@ -5164,7 +5180,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>381755.93838365644</v>
       </c>
@@ -5195,7 +5211,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>749715.90599999996</v>
       </c>
@@ -5218,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.34688091727946951</v>
+        <v>0.34688091727946946</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5793,13 +5809,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5822,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5875,6 +5891,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5891,17 +5918,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6017,397 +6033,397 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>2995441.59</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>3075203.75</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>2935836.83</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>1979548.12</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>1786257.6311000001</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>1471039.433</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>1105212.1177999999</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>1025253.7178</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>1199168.3252999999</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>1620150.6739000001</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>2641432.41</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>2758839.14</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>2689414.23</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>1778435.69</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>1616645.7855</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>1299577.5874999999</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>1012363.7751</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>821183.37919999997</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>1018326.6461</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>1144690.3533000001</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>39503.56</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>34325.129999999997</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>26009.279999999999</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>26199.42</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>25803.239300000001</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>27496.749400000001</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>30895.564999999999</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>89269.041400000002</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>96270.753700000001</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>122434.7022</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>3443.84</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>2062.65</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>1799.32</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>2220.02</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>2555.1316999999999</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>3583.8836999999999</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>1563.145</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>1398.3924</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>1304.7493999999999</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>1267.4317000000001</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>122733.73</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>118628.34</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>112193.53</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>92881.87</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>98270.921900000001</v>
       </c>
-      <c r="H8" s="334">
+      <c r="H8" s="321">
         <v>87435.0962</v>
       </c>
-      <c r="I8" s="334">
+      <c r="I8" s="321">
         <v>66949.809200000003</v>
       </c>
-      <c r="J8" s="334">
-        <v>0</v>
-      </c>
-      <c r="K8" s="334">
-        <v>0</v>
-      </c>
-      <c r="L8" s="334">
-        <v>0</v>
-      </c>
-      <c r="M8" s="334"/>
+      <c r="J8" s="321">
+        <v>0</v>
+      </c>
+      <c r="K8" s="321">
+        <v>0</v>
+      </c>
+      <c r="L8" s="321">
+        <v>0</v>
+      </c>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>1984.19</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>1109.03</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>1176.71</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>1802.32</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>493.37110000000001</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>97.840299999999999</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>87.729200000000006</v>
       </c>
-      <c r="J12" s="334"/>
-      <c r="K12" s="334"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>12457.09</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>5931.66</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>2216.44</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>2037.26</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>1480.8308</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>1809.4933000000001</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>5012.4776000000002</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>49136.31</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>28159.86</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>31269.46</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>20051.47</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>17391.0854</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>18009.5527</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>4894.3321999999998</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>13704.1828</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>30445.290099999998</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>60216.000999999997</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>218629.33</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>163033.85999999999</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>144968.98000000001</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>37199.29</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>36553.127500000002</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>2864.6253999999999</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>7983.8873999999996</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>48963.2163</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>131291.13870000001</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>341026.96950000001</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>2489.67</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>983.23</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>-771.93</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>219.4</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>223.20849999999999</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>71.949200000000005</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>6.0865999999999998</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>-142.3349</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>-239.5761</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>32.409500000000001</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6419,171 +6435,171 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>154945.9</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>143078.04</v>
       </c>
-      <c r="E19" s="334">
+      <c r="E19" s="321">
         <v>115739.41</v>
       </c>
-      <c r="F19" s="334">
+      <c r="F19" s="321">
         <v>108539.45</v>
       </c>
-      <c r="G19" s="334">
+      <c r="G19" s="321">
         <v>99339.8367</v>
       </c>
-      <c r="H19" s="334">
+      <c r="H19" s="321">
         <v>102341.4463</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="321">
         <v>102108.7965</v>
       </c>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>385024.86</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>512492.41</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>331348.71000000002</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>303321.95</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>202079.4627</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>-7480.7105000000001</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>37645.5429</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>53137.414700000001</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>328799.14020000002</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>362565.82380000001</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-310465.5</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-194997.95</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-181817.58</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-294554.96999999997</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-232655.17739999999</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>8162.0361000000003</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-296170.36139999999</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-64063.495300000002</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-53824.304799999998</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-51725.055200000003</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-77562.899999999994</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-105176.84</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-60642.84</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-46882.06</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>19076.583299999998</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-22204.614300000001</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-9192.5170999999991</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-162161.08549999999</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-117457.87</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>-173284.31940000001</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6620,186 +6636,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>779805.94000000006</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>614740.03</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>627070.1</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>565721.97</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>737082.00840000005</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>483752.78779999999</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>418633.2475</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>282078.32010000001</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>199277.88070000001</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>475355.28210000001</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>75410.259999999995</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>98279.37</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>130107.73</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>115109.66</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>101122.2853</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>512937.82659999997</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>289811.61910000001</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>169498.82380000001</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>161116.17800000001</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>169013.54149999999</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>1995570.48</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>1647330.89</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>1695609.48</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>1189596.92</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>1061667.9129999999</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>918370.71239999996</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>724476.08160000003</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>526758.79269999999</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>664276.83160000003</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>845128.23759999999</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>2827517.7899999996</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>2677835.46</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>2568258.0099999998</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>2275829.46</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>2266521.7039999999</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>2267283.5811000001</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>2290443.9753999999</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>2312836.8300999999</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>2316842.9693999998</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>2299154.9539000001</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>200865.76</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>198376.09</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>197959.04000000001</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>1622.36</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>1415.6996999999999</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>1219.5377000000001</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>1149.8104000000001</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>1128.896</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>1297.8493000000001</v>
       </c>
-      <c r="L32" s="334">
+      <c r="L32" s="321">
         <v>1509.1383000000001</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6826,47 +6842,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>2995441.59</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>3075203.75</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>2935836.83</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>1979548.12</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>1786257.6311000001</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>1471039.433</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>1105212.1177999999</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>1025253.7178</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>1199168.3252999999</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>1620150.6739000001</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6875,47 +6891,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-2641432.41</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-2758839.14</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-2689414.23</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-1778435.69</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-1616645.7855</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-1299577.5874999999</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-1012363.7751</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-821183.37919999997</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-1018326.6461</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-1144690.3533000001</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6924,47 +6940,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>354009.1799999997</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>316364.60999999987</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>246422.60000000009</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>201112.43000000017</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>169611.84560000012</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>171461.84550000005</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>92848.342699999921</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>204070.33860000002</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>180841.6791999999</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>475460.32059999998</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6973,47 +6989,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-39503.56</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-34325.129999999997</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-26009.279999999999</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-26199.42</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-25803.239300000001</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-27496.749400000001</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-30895.564999999999</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-89269.041400000002</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-96270.753700000001</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-122434.7022</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7022,47 +7038,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-3443.84</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-2062.65</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-1799.32</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-2220.02</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-2555.1316999999999</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-3583.8836999999999</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-1563.145</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-1398.3924</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-1304.7493999999999</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-1267.4317000000001</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7071,47 +7087,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-36059.72</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-32262.479999999996</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-24209.96</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-23979.399999999998</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-23248.107600000003</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-23912.865700000002</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-29332.42</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-87870.649000000005</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-94966.004300000001</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-121167.2705</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7120,47 +7136,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-122733.73</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-118628.34</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-112193.53</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-92881.87</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-98270.921900000001</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>-87435.0962</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>-66949.809200000003</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7169,47 +7185,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>191771.88999999972</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>163411.13999999987</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>108219.7900000001</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>82031.140000000189</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>45537.6844000001</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>56529.999900000053</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>-4997.0315000000846</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>114801.29720000002</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>84570.925499999896</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>353025.61839999998</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7316,47 +7332,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-49136.31</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-28159.86</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-31269.46</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-20051.47</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-17391.0854</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-18009.5527</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-4894.3321999999998</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-13704.1828</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-30445.290099999998</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-60216.000999999997</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7365,47 +7381,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>218629.33</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>163033.85999999999</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>144968.98000000001</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>37199.29</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>36553.127500000002</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>2864.6253999999999</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>7983.8873999999996</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>48963.2163</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>131291.13870000001</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>341026.96950000001</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7414,47 +7430,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-2489.67</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>-983.23</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>-219.4</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>-223.20849999999999</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>-71.949200000000005</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>-6.0865999999999998</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-32.409500000000001</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7468,47 +7484,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-1984.19</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-1109.03</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-1176.71</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-1802.32</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-493.37110000000001</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-97.840299999999999</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-87.729200000000006</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7517,47 +7533,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>12457.09</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>5931.66</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>2216.44</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>2037.26</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>1480.8308</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>1809.4933000000001</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>5012.4776000000002</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7773,47 +7789,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-154945.9</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-143078.04</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>-115739.41</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>-108539.45</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>-99339.8367</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>-102341.4463</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>-102108.7965</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7822,47 +7838,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-154945.9</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-143078.04</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-115739.41</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-108539.45</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-99339.8367</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>-102341.4463</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>-102108.7965</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7871,47 +7887,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7920,47 +7936,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-3003.5400000000081</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>212317.61999999997</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>88888.290000000037</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>-38115.079999999958</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>-11499.131399999984</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>-21523.288700000001</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>-267717.33559999999</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>-173087.16609999997</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>157516.96540000004</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>137556.4492</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8342,115 +8358,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>779805.94000000006</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>614740.03</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>627070.1</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>565721.97</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>737082.00840000005</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>483752.78779999999</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>75410.259999999995</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>98279.37</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>130107.73</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>115109.66</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>101122.2853</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>512937.82659999997</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>1995570.48</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>1647330.89</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>1695609.48</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>1189596.92</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>1061667.9129999999</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>918370.71239999996</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>724476.08160000003</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>526758.79269999999</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>664276.83160000003</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>845128.23759999999</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8459,47 +8475,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>2827517.7899999996</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>2677835.46</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>2568258.0099999998</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>2275829.46</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>2266521.7039999999</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>2267283.5811000001</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>2290443.9753999999</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>2312836.8300999999</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>2316842.9693999998</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>2299154.9539000001</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9583,11 +9599,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-241044.91095666669</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-224948.28161634356</v>
       </c>
@@ -9615,8 +9631,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>224948.28161634356</v>
       </c>
@@ -9920,54 +9936,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:J4)</f>
         <v>2746507.5724999998</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>2995441.59</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>3075203.75</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>2935836.83</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>1979548.12</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>1786257.6311000001</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>1471039.433</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>1105212.1177999999</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>1025253.7178</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>1199168.3252999999</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>1620150.6739000001</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9977,52 +9993,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-2469772.890416123</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-2644876.25</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-2760901.79</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-2691213.55</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-1780655.71</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-1619200.9172</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-1303161.4711999998</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-1013926.9201</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-822581.77159999998</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-1019631.3955</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-1145957.7850000001</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10032,52 +10048,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>276734.6820838768</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>350565.33999999985</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>314301.95999999996</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>244623.28000000026</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>198892.41000000015</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>167056.71390000009</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>167877.96180000016</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>91285.197699999902</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>202671.94620000001</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>179536.92979999993</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>474192.8888999999</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10087,52 +10103,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-140737.25750000001</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-158793.45000000001</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-150890.82</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-136403.49</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-116861.26999999999</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-121519.0295</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-111347.96189999999</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-96282.229200000002</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-87870.649000000005</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-94966.004300000001</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-121167.2705</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10142,54 +10158,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>135997.4245838768</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>191771.88999999984</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>163411.13999999996</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>108219.79000000027</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>82031.140000000159</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>45537.684400000086</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>56529.99990000017</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>-4997.0315000000992</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>114801.2972</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>84570.925499999925</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>353025.61839999992</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10199,52 +10215,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>154945.9</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>154945.9</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>143078.04</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>115739.41</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>108539.45</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>99339.8367</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>102341.4463</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>102108.7965</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10254,52 +10270,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-154945.9</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-154945.9</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-143078.04</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-115739.41</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-108539.45</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-99339.8367</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>-102341.4463</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>-102108.7965</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10309,54 +10325,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10366,52 +10382,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>2634.5367156970447</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>2634.5367156970447</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>1090.2570333626497</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-354.91850280927906</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-1046.963236195535</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>55.677897589888687</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>573.06719497553672</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>1770.7517295712728</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10421,52 +10437,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>138631.9612995738</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>194406.42671569684</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>164501.39703336256</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>107864.87149719099</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>80984.176763804615</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>45593.362297589956</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>57103.067094975719</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>-3226.2797704288264</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>114801.2972</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>84570.925499999925</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>353025.61839999992</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10476,52 +10492,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-34657.990324893457</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-49136.31</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-28159.86</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-31269.46</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-20051.47</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-17391.0854</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-18009.5527</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-4894.3321999999998</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-13704.1828</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-30445.290099999998</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-60216.000999999997</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10531,54 +10547,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-2282.7677664801586</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-2489.67</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>-983.23</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>-219.4</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>-223.20849999999999</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>-71.949200000000005</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>-6.0865999999999998</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>0</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>0</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-32.409500000000001</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10588,54 +10604,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>101691.20320820018</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>142780.44671569683</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>135358.30703336254</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>76595.411497191002</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>60713.306763804612</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>27979.068397589956</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>39021.565194975716</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>-8126.6985704288263</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>101097.11440000001</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>54125.635399999926</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>292777.20789999992</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10645,7 +10661,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10654,24 +10670,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10679,71 +10695,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>101691.20320820018</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>142780.44671569683</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>135358.30703336254</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>76595.411497191002</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>60713.306763804612</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>27979.068397589956</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>39021.565194975716</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>-8126.6985704288263</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>101097.11440000001</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>54125.635399999926</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>292777.20789999992</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10816,54 +10832,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-2467332.0764988102</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-2641432.41</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-2758839.14</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-2689414.23</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-1778435.69</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-1616645.7855</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-1299577.5874999999</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-1012363.7751</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-821183.37919999997</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-1018326.6461</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-1144690.3533000001</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10873,54 +10889,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-2440.8139173125619</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-3443.84</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-2062.65</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-1799.32</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-2220.02</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-2555.1316999999999</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-3583.8836999999999</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-1563.145</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-1398.3924</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-1304.7493999999999</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-1267.4317000000001</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10930,54 +10946,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-2469772.890416123</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-2644876.25</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-2760901.79</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-2691213.55</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-1780655.71</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-1619200.9172</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-1303161.4711999998</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-1013926.9201</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-822581.77159999998</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-1019631.3955</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-1145957.7850000001</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11183,54 +11199,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:J33)</f>
         <v>-29127.89</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-36059.72</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-32262.479999999996</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-24209.96</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-23979.399999999998</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-23248.107600000003</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-23912.865700000002</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-29332.42</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-87870.649000000005</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-94966.004300000001</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-121167.2705</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11240,7 +11256,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>-111609.36749999999</v>
       </c>
@@ -11249,47 +11265,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-122733.73</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-118628.34</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-112193.53</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-92881.87</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-98270.921900000001</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>-87435.0962</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>-66949.809200000003</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11299,54 +11315,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-140737.25750000001</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-158793.45000000001</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-150890.82</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-136403.49</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-116861.26999999999</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-121519.0295</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-111347.96189999999</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-96282.229200000002</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-87870.649000000005</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-94966.004300000001</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-121167.2705</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11640,52 +11656,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-1984.19</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-1984.19</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-1109.03</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-1176.71</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-1802.32</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-493.37110000000001</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-97.840299999999999</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-87.729200000000006</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11695,52 +11711,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>4618.7267156970447</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>4618.7267156970447</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>2199.2870333626497</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>821.79149719072097</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>755.35676380446489</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>549.0489975898887</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>670.90749497553668</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>1858.4809295712728</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11750,54 +11766,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>12457.09</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>12457.09</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>5931.66</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>2216.44</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>2037.26</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>1480.8308</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>1809.4933000000001</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>5012.4776000000002</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11807,52 +11823,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>2634.5367156970447</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>2634.5367156970447</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>1090.2570333626497</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-354.91850280927906</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-1046.963236195535</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>55.677897589888687</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>573.06719497553672</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>1770.7517295712728</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11999,52 +12015,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12054,52 +12070,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12109,52 +12125,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12164,52 +12180,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12219,53 +12235,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>65520.850000000297</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>22959.950000000099</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>66978.919999999896</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>-25015.320000000189</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>7419.0687999998991</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>-37367.474800000055</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>12950.502700000085</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-52133.898100000013</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>77165.503300000099</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>48217.352100000018</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12275,52 +12291,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>65520.850000000297</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>22959.950000000099</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>66978.919999999896</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>-25015.320000000189</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>7419.0687999998991</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>-37367.474800000055</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>12950.502700000085</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-52133.898100000013</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>77165.503300000099</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>48217.352100000018</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13695,54 +13711,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>4823088.2699999996</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>4823088.2699999996</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>4325166.3499999996</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>4263867.49</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>3465426.38</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>3328189.6169999996</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>3185654.2935000001</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>3014920.057</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>2839595.6228</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>2981119.801</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>3144283.1915000002</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13752,54 +13768,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>779805.94000000006</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>614740.03</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>627070.1</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>565721.97</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>737082.00840000005</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>483752.78779999999</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13809,54 +13825,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>75410.259999999995</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>98279.37</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>130107.73</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>115109.66</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>101122.2853</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>512937.82659999997</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13866,54 +13882,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>1995570.48</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>1995570.48</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>1647330.89</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>1695609.48</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>1189596.92</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>1061667.9129999999</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>918370.71239999996</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>724476.08160000003</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>526758.79269999999</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>664276.83160000003</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>845128.23759999999</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13923,54 +13939,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>2827517.7899999996</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>2827517.7899999996</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>2677835.46</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>2568258.0099999998</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>2275829.46</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>2266521.7039999999</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>2267283.5811000001</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>2290443.9753999999</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>2312836.8300999999</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>2316842.9693999998</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>2299154.9539000001</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15468,7 +15484,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15507,7 +15523,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>101691.20320820018</v>
       </c>
@@ -15539,7 +15555,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>1694853.3868033364</v>
       </c>
@@ -15547,17 +15563,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>72651.94</v>
       </c>
@@ -15565,15 +15581,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>381755.93838365644</v>
       </c>
@@ -15581,15 +15597,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>749715.90599999996</v>
       </c>
@@ -15597,15 +15613,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>2753673.291186993</v>
       </c>
@@ -15672,7 +15688,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15682,7 +15698,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15696,10 +15712,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15717,7 +15733,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15739,7 +15755,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15761,7 +15777,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15781,9 +15797,19 @@
         <f t="shared" si="1"/>
         <v>102080.45954349852</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15803,9 +15829,19 @@
         <f t="shared" si="1"/>
         <v>102210.54248648556</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15825,9 +15861,19 @@
         <f t="shared" si="1"/>
         <v>102340.79119647763</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15849,7 +15895,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15871,7 +15917,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15893,7 +15939,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15915,7 +15961,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15937,7 +15983,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15959,7 +16005,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15981,11 +16027,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16001,13 +16047,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16023,13 +16079,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16045,9 +16111,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16069,7 +16145,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16091,7 +16167,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16113,7 +16189,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16135,7 +16211,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16157,7 +16233,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16179,7 +16255,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16201,7 +16277,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16223,7 +16299,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16245,7 +16321,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16267,7 +16343,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16289,11 +16365,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16309,13 +16385,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16331,13 +16417,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16353,13 +16449,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16375,9 +16481,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16399,7 +16515,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16410,11 +16526,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16424,7 +16540,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2028526.1158511993</v>
@@ -16451,7 +16567,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16473,7 +16589,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16494,14 +16610,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>1694853.386803335</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>1773335.93203612</v>
       </c>
       <c r="D58" s="123">
@@ -16513,16 +16629,26 @@
       <c r="F58" s="123">
         <v>2855784.043374842</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>1694853.3868033355</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>1806381.5450048302</v>
       </c>
       <c r="D59" s="123">
@@ -16534,16 +16660,26 @@
       <c r="F59" s="123">
         <v>3650942.2694116104</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>1694853.3868033353</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>1839216.0489163534</v>
       </c>
       <c r="D60" s="123">
@@ -16555,16 +16691,26 @@
       <c r="F60" s="123">
         <v>4697585.6601613443</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>1694853.386803335</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>1870145.566212385</v>
       </c>
       <c r="D61" s="123">
@@ -16576,26 +16722,56 @@
       <c r="F61" s="123">
         <v>6024212.9296894623</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16967,6 +17143,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17069,7 +17315,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>1481153.858</v>
       </c>
@@ -17077,8 +17323,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18535,7 +18781,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>191771.88999999984</v>
       </c>
@@ -18543,11 +18789,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 海油工程(600583.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18560,7 +18806,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>142780.44671569683</v>
       </c>
@@ -18568,8 +18814,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18582,7 +18828,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>101691.20320820018</v>
       </c>
@@ -18590,8 +18836,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18601,8 +18847,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18615,8 +18861,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18634,8 +18880,8 @@
         <v>0.14806091180696912</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18652,8 +18898,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.32719702788845018</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18670,8 +18916,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.32982639766138688</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18697,21 +18943,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18725,8 +18971,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18740,8 +18986,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18761,8 +19007,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18772,8 +19018,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18787,8 +19033,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18798,8 +19044,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18819,8 +19065,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18830,8 +19076,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18845,8 +19091,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18856,8 +19102,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18877,8 +19123,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18888,8 +19134,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18903,8 +19149,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18915,8 +19161,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18978,8 +19224,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18989,8 +19235,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19004,8 +19250,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19015,8 +19261,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19036,8 +19282,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19047,8 +19293,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19062,8 +19308,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19073,8 +19319,8 @@
         <v>0.1</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19258,7 +19504,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19267,7 +19513,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.34688091727946951</v>
+        <v>0.34688091727946946</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98902AC0-E7A4-4680-B1BD-4F6822C814A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09BAE7A-5558-4530-97BD-05A1BA95D86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>5.18</v>
+        <v>5.15</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22902.617864</v>
+        <v>22769.977220000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4396,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14033403532037614</v>
+        <v>0.14261873641939782</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4527,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.4401563092944851E-2</v>
+        <v>4.4660212975039672E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8803088803088803E-2</v>
+        <v>3.9029126213592225E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.34688091727946946</v>
+        <v>0.34688091727946951</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,16 +13483,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8803088803088803E-2</v>
+        <v>3.9029126213592225E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8803088803088803E-2</v>
+        <v>3.9029126213592225E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.837837837837838E-2</v>
+        <v>2.8543689320388345E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.4401563092944851E-2</v>
+        <v>4.4660212975039672E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.2342413240073107E-2</v>
+        <v>6.270557292885022E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.9101674680661097E-2</v>
+        <v>5.9445956280742611E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3443954726935052E-2</v>
+        <v>3.3638773880684189E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.6509330559646726E-2</v>
+        <v>2.6663753844460198E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.2216537237679494E-2</v>
+        <v>1.2287701532267915E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.7038037060519904E-2</v>
+        <v>1.7137287761843319E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.5483710284504033E-3</v>
+        <v>-3.5690411509462306E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.4142165319411716E-2</v>
+        <v>4.4399304146515085E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3632946993836255E-2</v>
+        <v>2.3770614646227532E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12783569530722005</v>
+        <v>0.12858036926046598</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.546041037677945E-2</v>
+        <v>9.6016490437226709E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1185687578653817E-2</v>
+        <v>7.1600361486878983E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.329799539111762E-2</v>
+        <v>6.366672157786199E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.624237465817065E-2</v>
+        <v>1.6336990432878441E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5960239880462253E-2</v>
+        <v>1.6053212151610576E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2507851360096377E-3</v>
+        <v>1.2580712630155192E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4860152002752728E-3</v>
+        <v>3.5063220849370705E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1378873188537956E-2</v>
+        <v>2.1503410313908077E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7325821650446765E-2</v>
+        <v>5.7659758475594999E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14890305183672953</v>
+        <v>0.14977044825519592</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.18</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.18</v>
+        <v>5.15</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.34688091727946946</v>
+        <v>0.34688091727946951</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.18</v>
+        <v>5.15</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14033403532037614</v>
+        <v>0.14261873641939782</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AE8D37-F629-42D8-8955-6C4173E86681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91E0F2F-9066-DF40-AFC2-15908E9D68F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,7 +4340,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
@@ -4339,7 +4350,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4349,7 +4360,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4377,7 +4388,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4387,27 +4398,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4435,7 +4446,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4443,7 +4454,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4451,7 +4462,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4467,7 +4478,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4484,11 +4495,11 @@
         <v>0.13957647293979125</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4507,7 +4518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4523,10 +4534,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4545,7 +4556,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4564,7 +4575,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4583,11 +4594,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4597,25 +4608,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4624,16 +4635,16 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4646,20 +4657,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4672,7 +4683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4685,16 +4696,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4707,16 +4718,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4731,7 +4742,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4746,7 +4757,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4759,12 +4770,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4777,16 +4788,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4799,8 +4810,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4808,7 +4819,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4821,25 +4832,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4852,7 +4863,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4865,7 +4876,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
@@ -4875,7 +4886,7 @@
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
@@ -4891,7 +4902,7 @@
         <v>0.87391267559349473</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4902,7 +4913,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4915,7 +4926,7 @@
         <v>6.8755155989910458E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4929,7 +4940,7 @@
         <v>6.490075699179193E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4943,7 +4954,7 @@
         <v>0.62106298336522048</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4957,7 +4968,7 @@
         <v>1.7057676125178334</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4967,34 +4978,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5003,7 +5014,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5012,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5021,34 +5032,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5056,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5069,7 +5080,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5079,38 +5090,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5123,7 +5134,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5136,7 +5147,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5145,7 +5156,7 @@
         <v>2.5694600492681609E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5154,12 +5165,12 @@
         <v>0.53421555755411909</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5172,7 +5183,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5185,7 +5196,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5198,12 +5209,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5216,7 +5227,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5229,16 +5240,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5251,7 +5262,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5264,7 +5275,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5274,16 +5285,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5300,7 +5311,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5322,7 +5333,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5344,7 +5355,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5366,7 +5377,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5388,7 +5399,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5410,7 +5421,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5423,16 +5434,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5442,30 +5453,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5474,16 +5485,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5496,7 +5507,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5509,26 +5520,26 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.34688091727946946</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+        <v>0.34688091727946951</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5538,7 +5549,7 @@
         <v>2.9245294434498934</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5551,7 +5562,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5573,12 +5584,12 @@
         <v>0.53195802324569241</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5587,7 +5598,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5597,7 +5608,7 @@
         <v>0.43217519804432247</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5607,7 +5618,7 @@
         <v>4.1792472274204462</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5620,7 +5631,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5633,7 +5644,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5642,12 +5653,12 @@
         <v>0.34024196610342983</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5656,7 +5667,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5666,7 +5677,7 @@
         <v>0.53727540184178957</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5676,7 +5687,7 @@
         <v>5.8685745253612058</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5689,7 +5700,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5702,7 +5713,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5711,12 +5722,12 @@
         <v>8.3512512306442965E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5735,7 +5746,7 @@
         <v>0.51152290174831927</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5745,7 +5756,7 @@
         <v>5.4420382208736449</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5758,7 +5769,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5771,7 +5782,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5780,7 +5791,7 @@
         <v>0.14739695926290697</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5790,21 +5801,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5813,80 +5824,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5925,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5944,15 +5955,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6001,7 +6012,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6017,7 +6028,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6025,7 +6036,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6061,7 +6072,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6097,7 +6108,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6133,7 +6144,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6169,7 +6180,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6205,7 +6216,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6221,7 +6232,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6237,7 +6248,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6253,7 +6264,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6283,7 +6294,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6313,7 +6324,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6349,7 +6360,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6385,7 +6396,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6421,13 +6432,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6457,7 +6468,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6473,7 +6484,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6489,7 +6500,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6525,7 +6536,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6561,7 +6572,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6597,7 +6608,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6620,7 +6631,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6628,7 +6639,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6665,7 +6676,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6702,7 +6713,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6739,7 +6750,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6776,7 +6787,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6813,7 +6824,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6829,12 +6840,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6883,7 +6894,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6932,7 +6943,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6981,7 +6992,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7030,7 +7041,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7079,7 +7090,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7128,7 +7139,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7177,7 +7188,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7226,7 +7237,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7275,7 +7286,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7324,7 +7335,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7373,7 +7384,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7422,7 +7433,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7471,12 +7482,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7525,7 +7536,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7574,12 +7585,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7628,7 +7639,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7677,7 +7688,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7726,7 +7737,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7775,13 +7786,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7830,7 +7841,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7879,7 +7890,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7928,7 +7939,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7977,7 +7988,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8026,12 +8037,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8081,7 +8092,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8130,7 +8141,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8180,7 +8191,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8229,7 +8240,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8279,7 +8290,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8295,13 +8306,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8350,7 +8361,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8384,7 +8395,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8418,7 +8429,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8467,7 +8478,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8548,18 +8559,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8575,7 +8586,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8586,7 +8597,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8606,7 +8617,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8628,7 +8639,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8649,7 +8660,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8671,7 +8682,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8692,7 +8703,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8713,7 +8724,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8735,7 +8746,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8747,7 +8758,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8759,7 +8770,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8783,12 +8794,12 @@
         <v>1152452.19</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8808,7 +8819,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8828,7 +8839,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8848,7 +8859,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8868,7 +8879,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8888,7 +8899,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8909,7 +8920,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8929,7 +8940,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8949,7 +8960,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8961,7 +8972,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8973,7 +8984,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8997,7 +9008,7 @@
         <v>143297.514</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9014,7 +9025,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9033,7 +9044,7 @@
         <v>41368.748499999987</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9048,7 +9059,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9067,7 +9078,7 @@
         <v>-159497.01150000002</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9083,7 +9094,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9100,7 +9111,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9120,7 +9131,7 @@
         <v>2036939.2285</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9131,7 +9142,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9144,7 +9155,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9163,7 +9174,7 @@
         <v>741189.52450000006</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9179,7 +9190,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9195,7 +9206,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9211,7 +9222,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9230,7 +9241,7 @@
         <v>138977.209</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9250,7 +9261,7 @@
         <v>1295749.7039999999</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9270,7 +9281,7 @@
         <v>546033.79799999995</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9289,7 +9300,7 @@
         <v>749715.90599999996</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9300,7 +9311,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9314,7 +9325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9328,7 +9339,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9343,10 +9354,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9359,7 +9370,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9373,7 +9384,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9384,10 +9395,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9399,7 +9410,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9413,7 +9424,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9427,10 +9438,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9442,7 +9453,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9453,7 +9464,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9464,10 +9475,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9479,7 +9490,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9495,7 +9506,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9506,7 +9517,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9520,7 +9531,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9536,7 +9547,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9546,7 +9557,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9556,7 +9567,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9566,7 +9577,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9576,10 +9587,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9591,7 +9602,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9607,7 +9618,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9623,7 +9634,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9636,7 +9647,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9649,10 +9660,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9664,7 +9675,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9678,7 +9689,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9692,7 +9703,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9706,7 +9717,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9720,7 +9731,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9731,7 +9742,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9739,7 +9750,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9756,7 +9767,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9773,7 +9784,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9790,7 +9801,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9821,19 +9832,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9890,7 +9901,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9913,7 +9924,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9927,7 +9938,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9984,7 +9995,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10039,7 +10050,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10094,7 +10105,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10149,7 +10160,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10206,7 +10217,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10261,7 +10272,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10316,7 +10327,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10373,7 +10384,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10428,7 +10439,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10483,7 +10494,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10538,7 +10549,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10595,7 +10606,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10652,7 +10663,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10678,7 +10689,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10703,7 +10714,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10760,7 +10771,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10779,7 +10790,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10802,7 +10813,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10823,7 +10834,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10880,7 +10891,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10937,7 +10948,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10994,18 +11005,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11064,7 +11075,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11124,7 +11135,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11179,18 +11190,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11247,7 +11258,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11306,7 +11317,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11363,18 +11374,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11432,7 +11443,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11490,7 +11501,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11545,18 +11556,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11614,10 +11625,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11640,14 +11651,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11702,7 +11713,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11757,7 +11768,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11814,7 +11825,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11869,11 +11880,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11883,7 +11894,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11910,7 +11921,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11937,7 +11948,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11992,11 +12003,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12006,7 +12017,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12061,7 +12072,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12116,7 +12127,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12171,7 +12182,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12226,7 +12237,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12282,7 +12293,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12337,11 +12348,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12351,7 +12362,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12376,7 +12387,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12401,7 +12412,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12426,7 +12437,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12453,10 +12464,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12479,7 +12490,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12500,7 +12511,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12557,7 +12568,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12614,7 +12625,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12671,7 +12682,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12728,7 +12739,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12785,7 +12796,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12844,7 +12855,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12901,7 +12912,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12958,7 +12969,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13015,7 +13026,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13072,7 +13083,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13130,7 +13141,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13187,7 +13198,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13213,7 +13224,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13237,7 +13248,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13294,18 +13305,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13361,7 +13372,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13417,7 +13428,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13472,7 +13483,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
@@ -13527,11 +13538,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13552,7 +13563,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13609,7 +13620,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13666,10 +13677,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13692,7 +13703,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13702,7 +13713,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13759,7 +13770,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13816,7 +13827,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13873,7 +13884,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13930,7 +13941,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13987,11 +13998,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14014,7 +14025,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14071,7 +14082,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14128,7 +14139,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14155,18 +14166,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14218,7 +14229,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14270,11 +14281,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14328,7 +14339,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14383,7 +14394,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14437,7 +14448,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14493,7 +14504,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14550,7 +14561,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14569,7 +14580,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14592,7 +14603,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14613,7 +14624,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14671,7 +14682,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
@@ -14728,7 +14739,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
@@ -14778,688 +14789,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15481,16 +15492,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15502,7 +15513,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15515,7 +15526,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15536,7 +15547,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15547,7 +15558,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15565,7 +15576,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15581,7 +15592,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15597,7 +15608,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15613,7 +15624,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15627,7 +15638,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15641,7 +15652,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15655,10 +15666,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15668,13 +15679,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15684,7 +15695,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15694,7 +15705,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15708,10 +15719,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15729,7 +15740,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15751,7 +15762,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15773,7 +15784,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15805,7 +15816,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15837,7 +15848,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15869,7 +15880,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15891,7 +15902,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15913,7 +15924,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15935,7 +15946,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15957,7 +15968,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15979,7 +15990,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16001,7 +16012,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16023,7 +16034,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16055,7 +16066,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16087,7 +16098,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16119,7 +16130,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16141,7 +16152,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16163,7 +16174,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16185,7 +16196,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16207,7 +16218,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16229,7 +16240,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16251,7 +16262,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16273,7 +16284,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16295,7 +16306,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16317,7 +16328,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16339,7 +16350,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16361,7 +16372,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16393,7 +16404,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16425,7 +16436,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16457,7 +16468,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16489,7 +16500,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16511,7 +16522,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16522,11 +16533,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16536,7 +16547,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2028526.1158511993</v>
@@ -16563,7 +16574,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16585,7 +16596,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16606,7 +16617,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16637,7 +16648,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16668,7 +16679,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16699,7 +16710,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16730,7 +16741,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16747,7 +16758,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16767,7 +16778,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16790,7 +16801,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16816,7 +16827,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16843,7 +16854,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16870,7 +16881,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16897,7 +16908,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16924,7 +16935,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16950,7 +16961,7 @@
         <v>13.019551302566807</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16976,7 +16987,7 @@
         <v>16.020050763791041</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16993,7 +17004,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17015,7 +17026,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17038,7 +17049,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17061,7 +17072,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17084,7 +17095,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17106,14 +17117,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17121,26 +17132,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17154,7 +17165,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17168,7 +17179,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17182,7 +17193,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17196,7 +17207,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17241,16 +17252,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17262,7 +17273,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17275,7 +17286,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17296,7 +17307,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17307,7 +17318,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17323,7 +17334,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17337,10 +17348,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17350,13 +17361,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17366,7 +17377,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17376,7 +17387,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17390,10 +17401,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17411,7 +17422,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17433,7 +17444,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17455,7 +17466,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17477,7 +17488,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17499,7 +17510,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17521,7 +17532,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17543,7 +17554,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17565,7 +17576,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17587,7 +17598,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17609,7 +17620,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17631,7 +17642,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17653,7 +17664,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17675,7 +17686,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17697,7 +17708,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17719,7 +17730,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17741,7 +17752,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17763,7 +17774,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17785,7 +17796,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17807,7 +17818,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17829,7 +17840,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17851,7 +17862,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17873,7 +17884,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17895,7 +17906,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17917,7 +17928,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17939,7 +17950,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17961,7 +17972,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17983,7 +17994,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18005,7 +18016,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18027,7 +18038,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18049,7 +18060,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18071,7 +18082,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18093,7 +18104,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18104,11 +18115,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18118,7 +18129,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>1772754.6854148009</v>
@@ -18145,7 +18156,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18167,7 +18178,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18188,7 +18199,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18209,7 +18220,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18230,7 +18241,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18251,7 +18262,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18272,14 +18283,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18289,7 +18300,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18312,7 +18323,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18338,7 +18349,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18365,7 +18376,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18392,7 +18403,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18419,7 +18430,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18446,7 +18457,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18472,7 +18483,7 @@
         <v>9.2851169806622025</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18498,7 +18509,7 @@
         <v>11.90729149293751</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18515,7 +18526,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18537,7 +18548,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18560,7 +18571,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18583,7 +18594,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18606,7 +18617,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18628,14 +18639,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18643,23 +18654,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18689,17 +18700,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18712,7 +18723,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18724,7 +18735,7 @@
         <v>-5.19</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18744,7 +18755,7 @@
         <v>0.20099999999999998</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18753,7 +18764,7 @@
         <v>0.20099999999999998</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18773,7 +18784,7 @@
         <v>7.1905661568976029</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18798,7 +18809,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18820,7 +18831,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18842,7 +18853,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18853,7 +18864,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18867,7 +18878,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18886,7 +18897,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18904,7 +18915,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18915,7 +18926,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18924,7 +18935,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18932,7 +18943,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18944,18 +18955,18 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
@@ -18970,7 +18981,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18985,7 +18996,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18994,7 +19005,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19006,7 +19017,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19017,7 +19028,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19032,7 +19043,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19043,7 +19054,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19052,7 +19063,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19064,7 +19075,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19075,7 +19086,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19090,7 +19101,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19101,7 +19112,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19110,7 +19121,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19122,7 +19133,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19133,7 +19144,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19148,7 +19159,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19160,7 +19171,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19173,7 +19184,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19182,12 +19193,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19197,12 +19208,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19211,7 +19222,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19223,7 +19234,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19234,7 +19245,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19249,7 +19260,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19260,7 +19271,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19269,7 +19280,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19281,7 +19292,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19292,7 +19303,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19307,7 +19318,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19318,7 +19329,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19338,7 +19349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19347,7 +19358,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19355,7 +19366,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19368,7 +19379,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19380,7 +19391,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19396,7 +19407,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19404,7 +19415,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19414,7 +19425,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19426,7 +19437,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19436,7 +19447,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19452,7 +19463,7 @@
         <v>0.34262299719893202</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19461,12 +19472,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19476,7 +19487,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19489,33 +19500,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.34688091727946946</v>
+        <v>0.34688091727946951</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19525,7 +19536,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19545,15 +19556,15 @@
         <v>0.53195802324569241</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
@@ -19566,7 +19577,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
@@ -19575,15 +19586,15 @@
         <v>0.13957647293979125</v>
       </c>
     </row>
-    <row r="88" spans="2:8">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19592,7 +19603,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19604,7 +19615,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19614,7 +19625,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19634,14 +19645,14 @@
         <v>0.34024196610342983</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19652,7 +19663,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19664,7 +19675,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19676,7 +19687,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19695,15 +19706,15 @@
         <v>8.3512512306442965E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19712,7 +19723,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19722,7 +19733,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19732,7 +19743,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19751,16 +19762,16 @@
         <v>0.14739695926290697</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19768,7 +19779,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19776,7 +19787,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91E0F2F-9066-DF40-AFC2-15908E9D68F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AA4F50-DFB5-4A1B-8B9D-BCECDC4E23B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2513,7 +2502,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3905,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3943,7 +3932,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4232,7 +4221,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4241,7 +4230,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4272,7 +4261,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4281,7 +4270,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +4287,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4308,7 +4297,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4318,17 +4307,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4340,17 +4329,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.19</v>
+        <v>5.26</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4360,13 +4349,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22946.831412</v>
+        <v>23256.326248000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4388,7 +4377,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4398,27 +4387,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4433,7 +4422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4446,7 +4435,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4454,7 +4443,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4462,7 +4451,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4478,7 +4467,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4492,14 +4481,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13957647293979125</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.13432867044450703</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4518,7 +4507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4537,7 +4526,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4556,7 +4545,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4575,7 +4564,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4594,11 +4583,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4608,25 +4597,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4635,16 +4624,16 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4657,20 +4646,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4683,7 +4672,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4696,16 +4685,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4718,16 +4707,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4742,7 +4731,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4757,7 +4746,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4770,12 +4759,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4788,16 +4777,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4810,8 +4799,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,7 +4808,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4832,25 +4821,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4863,7 +4852,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4876,23 +4865,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.4316010948257094E-2</v>
+        <v>4.3726254148565458E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.872832369942196E-2</v>
+        <v>3.821292775665399E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4902,7 +4891,7 @@
         <v>0.87391267559349473</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4913,7 +4902,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4926,7 +4915,7 @@
         <v>6.8755155989910458E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4940,7 +4929,7 @@
         <v>6.490075699179193E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4954,7 +4943,7 @@
         <v>0.62106298336522048</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4968,7 +4957,7 @@
         <v>1.7057676125178334</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4978,34 +4967,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5014,7 +5003,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5023,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5032,34 +5021,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5067,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5080,7 +5069,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5090,38 +5079,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5134,7 +5123,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5147,7 +5136,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5156,7 +5145,7 @@
         <v>2.5694600492681609E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5165,12 +5154,12 @@
         <v>0.53421555755411909</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5183,7 +5172,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5196,7 +5185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5209,12 +5198,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5227,7 +5216,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5240,16 +5229,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5262,7 +5251,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5275,7 +5264,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5285,16 +5274,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5311,7 +5300,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5333,7 +5322,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5355,7 +5344,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5377,7 +5366,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5399,7 +5388,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5421,7 +5410,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5434,16 +5423,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5453,30 +5442,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5485,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5494,7 +5483,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5507,7 +5496,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5520,7 +5509,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5529,7 +5518,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5539,7 +5528,7 @@
         <v>0.34688091727946951</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5549,7 +5538,7 @@
         <v>2.9245294434498934</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5562,7 +5551,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5584,12 +5573,12 @@
         <v>0.53195802324569241</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5598,7 +5587,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5608,7 +5597,7 @@
         <v>0.43217519804432247</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5618,7 +5607,7 @@
         <v>4.1792472274204462</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5631,7 +5620,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5644,7 +5633,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5653,12 +5642,12 @@
         <v>0.34024196610342983</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5667,7 +5656,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5677,7 +5666,7 @@
         <v>0.53727540184178957</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5687,7 +5676,7 @@
         <v>5.8685745253612058</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5700,7 +5689,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5713,7 +5702,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5722,12 +5711,12 @@
         <v>8.3512512306442965E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5736,7 +5725,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5746,7 +5735,7 @@
         <v>0.51152290174831927</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5756,7 +5745,7 @@
         <v>5.4420382208736449</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5769,7 +5758,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5782,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5791,7 +5780,7 @@
         <v>0.14739695926290697</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5801,21 +5790,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5824,91 +5813,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5925,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5955,15 +5944,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6012,7 +6001,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6028,7 +6017,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6036,7 +6025,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6072,7 +6061,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6108,7 +6097,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6144,7 +6133,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6180,7 +6169,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6216,7 +6205,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6232,7 +6221,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6248,7 +6237,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6264,7 +6253,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6294,7 +6283,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6324,7 +6313,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6360,7 +6349,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6396,7 +6385,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6432,13 +6421,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6468,7 +6457,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6484,7 +6473,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6500,7 +6489,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6536,7 +6525,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6572,7 +6561,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6608,7 +6597,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6631,7 +6620,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6639,7 +6628,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6676,7 +6665,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6713,7 +6702,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6750,7 +6739,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6787,7 +6776,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6824,7 +6813,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6840,12 +6829,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6894,7 +6883,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6943,7 +6932,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6992,7 +6981,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7041,7 +7030,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7090,7 +7079,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7139,7 +7128,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7188,7 +7177,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7237,7 +7226,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7286,7 +7275,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7335,7 +7324,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7384,7 +7373,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7433,7 +7422,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7482,12 +7471,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7536,7 +7525,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7585,12 +7574,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7639,7 +7628,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7688,7 +7677,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7737,7 +7726,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7786,13 +7775,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7841,7 +7830,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7890,7 +7879,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7939,7 +7928,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7988,7 +7977,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8037,12 +8026,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8092,7 +8081,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8141,7 +8130,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8191,7 +8180,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8240,7 +8229,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8290,7 +8279,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8306,13 +8295,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8361,7 +8350,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8395,7 +8384,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8429,7 +8418,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8478,7 +8467,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8559,7 +8548,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8570,7 +8559,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8586,7 +8575,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8597,7 +8586,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8617,7 +8606,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8639,7 +8628,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8660,7 +8649,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8682,7 +8671,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8703,7 +8692,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8724,7 +8713,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8746,7 +8735,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8758,7 +8747,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8770,7 +8759,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8794,12 +8783,12 @@
         <v>1152452.19</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8819,7 +8808,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8839,7 +8828,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8859,7 +8848,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8879,7 +8868,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8899,7 +8888,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8920,7 +8909,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8940,7 +8929,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8960,7 +8949,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8972,7 +8961,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8984,7 +8973,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9008,7 +8997,7 @@
         <v>143297.514</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9025,7 +9014,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9044,7 +9033,7 @@
         <v>41368.748499999987</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9059,7 +9048,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9078,7 +9067,7 @@
         <v>-159497.01150000002</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9094,7 +9083,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9111,7 +9100,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9131,7 +9120,7 @@
         <v>2036939.2285</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9142,7 +9131,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9155,7 +9144,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9174,7 +9163,7 @@
         <v>741189.52450000006</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9190,7 +9179,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9206,7 +9195,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9222,7 +9211,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9241,7 +9230,7 @@
         <v>138977.209</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9261,7 +9250,7 @@
         <v>1295749.7039999999</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9281,7 +9270,7 @@
         <v>546033.79799999995</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9300,7 +9289,7 @@
         <v>749715.90599999996</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9311,7 +9300,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9325,7 +9314,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9339,7 +9328,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9354,10 +9343,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9370,7 +9359,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9384,7 +9373,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9395,10 +9384,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9410,7 +9399,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9424,7 +9413,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9438,10 +9427,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9453,7 +9442,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9464,7 +9453,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9475,10 +9464,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9490,7 +9479,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9506,7 +9495,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9517,7 +9506,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9531,7 +9520,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9547,7 +9536,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9557,7 +9546,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9567,7 +9556,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9577,7 +9566,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9587,10 +9576,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9602,7 +9591,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9618,7 +9607,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9634,7 +9623,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9647,7 +9636,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9660,10 +9649,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9675,7 +9664,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9689,7 +9678,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9703,7 +9692,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9717,7 +9706,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9731,7 +9720,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9742,7 +9731,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9750,7 +9739,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9767,7 +9756,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9784,7 +9773,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9801,7 +9790,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9832,19 +9821,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9901,7 +9890,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9924,7 +9913,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9938,7 +9927,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9995,7 +9984,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10050,7 +10039,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10105,7 +10094,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10160,7 +10149,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10217,7 +10206,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10272,7 +10261,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10327,7 +10316,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10384,7 +10373,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10439,7 +10428,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10494,7 +10483,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10549,7 +10538,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10606,7 +10595,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10663,7 +10652,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10689,7 +10678,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10714,7 +10703,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10771,7 +10760,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10790,7 +10779,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10813,7 +10802,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10834,7 +10823,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10891,7 +10880,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10948,7 +10937,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11005,18 +10994,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11075,7 +11064,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11135,7 +11124,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11190,18 +11179,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11258,7 +11247,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11317,7 +11306,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11374,18 +11363,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11443,7 +11432,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11501,7 +11490,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11556,18 +11545,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11625,10 +11614,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11651,14 +11640,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11713,7 +11702,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11768,7 +11757,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11825,7 +11814,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11880,11 +11869,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11894,7 +11883,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11921,7 +11910,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11948,7 +11937,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -12003,11 +11992,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12017,7 +12006,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12072,7 +12061,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12127,7 +12116,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12182,7 +12171,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12237,7 +12226,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12293,7 +12282,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12348,11 +12337,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12362,7 +12351,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12387,7 +12376,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12412,7 +12401,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12437,7 +12426,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12464,10 +12453,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12490,7 +12479,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12511,7 +12500,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12568,7 +12557,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12625,7 +12614,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12682,7 +12671,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12739,7 +12728,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12796,7 +12785,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12855,7 +12844,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12912,7 +12901,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12969,7 +12958,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13026,7 +13015,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13083,7 +13072,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13141,7 +13130,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13198,7 +13187,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13224,7 +13213,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13248,7 +13237,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13305,18 +13294,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13372,7 +13361,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13428,7 +13417,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13483,23 +13472,23 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.872832369942196E-2</v>
+        <v>3.821292775665399E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.872832369942196E-2</v>
+        <v>3.821292775665399E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8323699421965314E-2</v>
+        <v>2.7946768060836503E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -13538,11 +13527,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13563,7 +13552,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13620,7 +13609,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13677,10 +13666,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13703,7 +13692,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13713,7 +13702,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13770,7 +13759,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13827,7 +13816,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13884,7 +13873,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13941,7 +13930,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13998,11 +13987,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14025,7 +14014,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14082,7 +14071,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14139,7 +14128,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14166,18 +14155,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14229,7 +14218,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14281,11 +14270,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14339,7 +14328,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14394,7 +14383,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14448,7 +14437,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14504,7 +14493,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14561,7 +14550,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14580,7 +14569,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14603,7 +14592,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14624,7 +14613,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14682,795 +14671,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.4316010948257094E-2</v>
+        <v>4.3726254148565458E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.2222292983348484E-2</v>
+        <v>6.1394239654672757E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.8987798621546135E-2</v>
+        <v>5.820278989464344E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3379515507808009E-2</v>
+        <v>3.2935301423103344E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.6458252851439309E-2</v>
+        <v>2.6106146824899246E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.2192998630285119E-2</v>
+        <v>1.2030734389958131E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.7005208472734699E-2</v>
+        <v>1.6778903417013897E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.541534090052618E-3</v>
+        <v>-3.4944034082458344E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.4057112977755816E-2</v>
+        <v>4.3470801588318002E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3587411450495529E-2</v>
+        <v>2.3273510537656236E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12758938375556836</v>
+        <v>0.12589142617707222</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5276478950234597E-2</v>
+        <v>9.4008541017436803E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1048528257693019E-2</v>
+        <v>7.0103015524225626E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3176033935643403E-2</v>
+        <v>6.2335288236880088E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6211079138598067E-2</v>
+        <v>1.5995342343977939E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5929487973178124E-2</v>
+        <v>1.571749858950465E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2483751453814882E-3</v>
+        <v>1.2317617879334455E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4792984079818714E-3</v>
+        <v>3.4329959576855349E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1337680754648671E-2</v>
+        <v>2.1053719223693271E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.721536727347095E-2</v>
+        <v>5.6453946035991298E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14861614807596513</v>
+        <v>0.14663836663769184</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15492,16 +15481,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15513,7 +15502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15526,7 +15515,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15547,7 +15536,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15558,7 +15547,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15576,7 +15565,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15592,7 +15581,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15608,7 +15597,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15624,7 +15613,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15638,7 +15627,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15652,7 +15641,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15666,10 +15655,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15679,13 +15668,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15695,7 +15684,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15705,7 +15694,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15719,10 +15708,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15740,7 +15729,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15762,7 +15751,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15784,7 +15773,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15816,7 +15805,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15848,7 +15837,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15880,7 +15869,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15902,7 +15891,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15924,7 +15913,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15946,7 +15935,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15968,7 +15957,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15990,7 +15979,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16012,7 +16001,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16034,7 +16023,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16066,7 +16055,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16098,7 +16087,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16130,7 +16119,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16152,7 +16141,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16174,7 +16163,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16196,7 +16185,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16218,7 +16207,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16240,7 +16229,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16262,7 +16251,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16284,7 +16273,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16306,7 +16295,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16328,7 +16317,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16350,7 +16339,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16372,7 +16361,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16404,7 +16393,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16436,7 +16425,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16468,7 +16457,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16500,7 +16489,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16522,7 +16511,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16533,11 +16522,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16547,7 +16536,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2028526.1158511993</v>
@@ -16574,7 +16563,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16596,7 +16585,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16617,7 +16606,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16648,7 +16637,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16679,7 +16668,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16710,7 +16699,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16741,7 +16730,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16758,7 +16747,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16778,7 +16767,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16801,7 +16790,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16827,7 +16816,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16854,7 +16843,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16881,7 +16870,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16908,7 +16897,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16935,7 +16924,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16961,7 +16950,7 @@
         <v>13.019551302566807</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16987,7 +16976,7 @@
         <v>16.020050763791041</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -17004,7 +16993,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17026,7 +17015,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17049,7 +17038,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17072,7 +17061,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17095,7 +17084,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17117,14 +17106,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17132,26 +17121,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17165,7 +17154,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17179,7 +17168,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17193,7 +17182,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17207,7 +17196,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17252,16 +17241,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17273,7 +17262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17286,7 +17275,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17307,7 +17296,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17318,7 +17307,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17334,7 +17323,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17348,10 +17337,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17361,13 +17350,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17377,7 +17366,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17387,7 +17376,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17401,10 +17390,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17422,7 +17411,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17444,7 +17433,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17466,7 +17455,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17488,7 +17477,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17510,7 +17499,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17532,7 +17521,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17554,7 +17543,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17576,7 +17565,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17598,7 +17587,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17620,7 +17609,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17642,7 +17631,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17664,7 +17653,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17686,7 +17675,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17708,7 +17697,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17730,7 +17719,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17752,7 +17741,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17774,7 +17763,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17796,7 +17785,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17818,7 +17807,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17840,7 +17829,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17862,7 +17851,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17884,7 +17873,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17906,7 +17895,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17928,7 +17917,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17950,7 +17939,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17972,7 +17961,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17994,7 +17983,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18016,7 +18005,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18038,7 +18027,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18060,7 +18049,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18082,7 +18071,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18104,7 +18093,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18115,11 +18104,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18129,7 +18118,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>1772754.6854148009</v>
@@ -18156,7 +18145,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18178,7 +18167,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18199,7 +18188,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18220,7 +18209,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18241,7 +18230,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18262,7 +18251,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18283,14 +18272,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18300,7 +18289,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18323,7 +18312,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18349,7 +18338,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18376,7 +18365,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18403,7 +18392,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18430,7 +18419,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18457,7 +18446,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18483,7 +18472,7 @@
         <v>9.2851169806622025</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18509,7 +18498,7 @@
         <v>11.90729149293751</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18526,7 +18515,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18548,7 +18537,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18571,7 +18560,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18594,7 +18583,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18617,7 +18606,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18639,14 +18628,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18654,23 +18643,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18700,7 +18689,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18710,7 +18699,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18723,7 +18712,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18732,10 +18721,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.19</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-5.26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18755,7 +18744,7 @@
         <v>0.20099999999999998</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18764,7 +18753,7 @@
         <v>0.20099999999999998</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18784,7 +18773,7 @@
         <v>7.1905661568976029</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18809,7 +18798,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18831,7 +18820,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18853,7 +18842,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18864,7 +18853,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18878,7 +18867,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18897,7 +18886,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18915,7 +18904,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18926,7 +18915,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18935,7 +18924,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18943,7 +18932,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18955,24 +18944,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.19</v>
+        <v>5.26</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18981,7 +18970,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18996,7 +18985,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -19005,7 +18994,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19017,7 +19006,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19028,7 +19017,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19043,7 +19032,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19054,7 +19043,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19063,7 +19052,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19075,7 +19064,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19086,7 +19075,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19101,7 +19090,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19112,7 +19101,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19121,7 +19110,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19133,7 +19122,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19144,7 +19133,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19159,7 +19148,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19171,7 +19160,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19184,7 +19173,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19193,12 +19182,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19208,12 +19197,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19222,7 +19211,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19234,7 +19223,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19245,7 +19234,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19260,7 +19249,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19271,7 +19260,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19280,7 +19269,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19292,7 +19281,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19303,7 +19292,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19318,7 +19307,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19329,7 +19318,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19349,7 +19338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19358,7 +19347,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19366,7 +19355,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19379,7 +19368,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19391,7 +19380,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19407,7 +19396,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19415,7 +19404,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19425,7 +19414,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19437,7 +19426,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19447,7 +19436,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19463,7 +19452,7 @@
         <v>0.34262299719893202</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19472,12 +19461,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19487,7 +19476,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19500,12 +19489,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19514,7 +19503,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19526,7 +19515,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19536,7 +19525,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19556,45 +19545,45 @@
         <v>0.53195802324569241</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.19</v>
+        <v>5.26</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13957647293979125</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.13432867044450703</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19603,7 +19592,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19615,7 +19604,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19625,7 +19614,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19645,14 +19634,14 @@
         <v>0.34024196610342983</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19663,7 +19652,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19675,7 +19664,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19687,7 +19676,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19706,15 +19695,15 @@
         <v>8.3512512306442965E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19723,7 +19712,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19733,7 +19722,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19743,7 +19732,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19762,16 +19751,16 @@
         <v>0.14739695926290697</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19779,7 +19768,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19787,7 +19776,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AA4F50-DFB5-4A1B-8B9D-BCECDC4E23B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC183283-9359-4328-B074-4B7F06E0EFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC183283-9359-4328-B074-4B7F06E0EFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F044D08-1181-4728-8862-809909DBBAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.26</v>
+        <v>5.23</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23256.326248000001</v>
+        <v>23123.685603999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13432867044450703</v>
+        <v>0.13656600369515881</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.3726254148565458E-2</v>
+        <v>4.3977073962037157E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.821292775665399E-2</v>
+        <v>3.8432122370936898E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13479,16 +13479,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.821292775665399E-2</v>
+        <v>3.8432122370936898E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.821292775665399E-2</v>
+        <v>3.8432122370936898E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.7946768060836503E-2</v>
+        <v>2.810707456978967E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14678,50 +14678,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3726254148565458E-2</v>
+        <v>4.3977073962037157E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.1394239654672757E-2</v>
+        <v>6.1746405465311405E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.820278989464344E-2</v>
+        <v>5.8536649110100279E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.2935301423103344E-2</v>
+        <v>3.3124222846180412E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.6106146824899246E-2</v>
+        <v>2.6255895277049718E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.2030734389958131E-2</v>
+        <v>1.20997443386577E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6778903417013897E-2</v>
+        <v>1.6875149516920283E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.4944034082458344E-3</v>
+        <v>-3.5144477872606286E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.3470801588318002E-2</v>
+        <v>4.372015609073665E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3273510537656236E-2</v>
+        <v>2.3407010598101682E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12589142617707222</v>
+        <v>0.12661355672875713</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14735,43 +14735,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4008541017436803E-2</v>
+        <v>9.4547786950615206E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0103015524225626E-2</v>
+        <v>7.0505136072165728E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2335288236880088E-2</v>
+        <v>6.2692852031737911E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5995342343977939E-2</v>
+        <v>1.6087093829698654E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.571749858950465E-2</v>
+        <v>1.5807656325199707E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2317617879334455E-3</v>
+        <v>1.2388273431223563E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4329959576855349E-3</v>
+        <v>3.452688095110117E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1053719223693271E-2</v>
+        <v>2.1174486255569142E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6453946035991298E-2</v>
+        <v>5.6777773642316294E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14663836663769184</v>
+        <v>0.14747950449603422</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.26</v>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.26</v>
+        <v>5.23</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.26</v>
+        <v>5.23</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13432867044450703</v>
+        <v>0.13656600369515881</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F044D08-1181-4728-8862-809909DBBAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0791E47D-D5D1-4F76-97C3-63807FE56071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0791E47D-D5D1-4F76-97C3-63807FE56071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267518D1-50DD-47F0-8B05-4EE485C7F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23123.685603999998</v>
+        <v>23035.258507999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13656600369515881</v>
+        <v>0.13806730030798309</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.3977073962037157E-2</v>
+        <v>4.4145891904309849E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8432122370936898E-2</v>
+        <v>3.8579654510556616E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13479,16 +13479,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8432122370936898E-2</v>
+        <v>3.8579654510556616E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8432122370936898E-2</v>
+        <v>3.8579654510556616E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.810707456978967E-2</v>
+        <v>2.8214971209213052E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14678,50 +14678,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3977073962037157E-2</v>
+        <v>4.4145891904309849E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.1746405465311405E-2</v>
+        <v>6.1983435812587077E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.8536649110100279E-2</v>
+        <v>5.8761357935858821E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3124222846180412E-2</v>
+        <v>3.3251379171885524E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.6255895277049718E-2</v>
+        <v>2.6356685661990408E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.20997443386577E-2</v>
+        <v>1.2146192493508593E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6875149516920283E-2</v>
+        <v>1.6939929361514987E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.5144477872606286E-3</v>
+        <v>-3.5279389495917637E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.372015609073665E-2</v>
+        <v>4.3887987783983243E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3407010598101682E-2</v>
+        <v>2.3496864765464837E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12661355672875713</v>
+        <v>0.12709959725362763</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14735,43 +14735,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4547786950615206E-2</v>
+        <v>9.4910734309350778E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0505136072165728E-2</v>
+        <v>7.0775789185686513E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2692852031737911E-2</v>
+        <v>6.2933515571207146E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6087093829698654E-2</v>
+        <v>1.614884850850748E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5807656325199707E-2</v>
+        <v>1.5868338307254218E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2388273431223563E-3</v>
+        <v>1.2435829183358778E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.452688095110117E-3</v>
+        <v>3.4659421760894265E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1174486255569142E-2</v>
+        <v>2.1255770271905297E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6777773642316294E-2</v>
+        <v>5.6995730546893324E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14747950449603422</v>
+        <v>0.14804564462845662</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.23</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13656600369515881</v>
+        <v>0.13806730030798309</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267518D1-50DD-47F0-8B05-4EE485C7F9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CF3E4C-73DE-4DE5-8134-E7470571D09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23035.258507999999</v>
+        <v>23079.472055999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13806730030798309</v>
+        <v>0.13731567198142991</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.4145891904309849E-2</v>
+        <v>4.4061321230163666E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8579654510556616E-2</v>
+        <v>3.8505747126436778E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13479,16 +13479,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8579654510556616E-2</v>
+        <v>3.8505747126436778E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8579654510556616E-2</v>
+        <v>3.8505747126436778E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8214971209213052E-2</v>
+        <v>2.8160919540229885E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14678,50 +14678,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.4145891904309849E-2</v>
+        <v>4.4061321230163666E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.1983435812587077E-2</v>
+        <v>6.186469359838672E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.8761357935858821E-2</v>
+        <v>5.8648788284640707E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3251379171885524E-2</v>
+        <v>3.3187679211786128E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.6356685661990408E-2</v>
+        <v>2.6306193927005755E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.2146192493508593E-2</v>
+        <v>1.2122923925513366E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6939929361514987E-2</v>
+        <v>1.6907477389558064E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.5279389495917637E-3</v>
+        <v>-3.5211804458569135E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.3887987783983243E-2</v>
+        <v>4.3803911179033088E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3496864765464837E-2</v>
+        <v>2.3451851614573142E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12709959725362763</v>
+        <v>0.12685611143513409</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14735,43 +14735,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4910734309350778E-2</v>
+        <v>9.472891297925623E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0775789185686513E-2</v>
+        <v>7.06402033826488E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2933515571207146E-2</v>
+        <v>6.2812953280840855E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.614884850850748E-2</v>
+        <v>1.6117912017111869E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5868338307254218E-2</v>
+        <v>1.5837939191723077E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2435829183358778E-3</v>
+        <v>1.2412005755804451E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4659421760894265E-3</v>
+        <v>3.4593024401199067E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1255770271905297E-2</v>
+        <v>2.1215050405484024E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6995730546893324E-2</v>
+        <v>5.6886543323623417E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14804564462845662</v>
+        <v>0.1477620322824251</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.21</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13806730030798309</v>
+        <v>0.13731567198142991</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CF3E4C-73DE-4DE5-8134-E7470571D09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5663AF8C-82FC-4290-A0E0-F1DCBEC6FF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23079.472055999999</v>
+        <v>22991.044959999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13731567198142991</v>
+        <v>0.13882089762469163</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.4061321230163666E-2</v>
+        <v>4.4230787850279681E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8505747126436778E-2</v>
+        <v>3.865384615384615E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13479,16 +13479,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8505747126436778E-2</v>
+        <v>3.865384615384615E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8505747126436778E-2</v>
+        <v>3.865384615384615E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8160919540229885E-2</v>
+        <v>2.8269230769230765E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14678,50 +14678,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.4061321230163666E-2</v>
+        <v>4.4230787850279681E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.186469359838672E-2</v>
+        <v>6.2102634727611281E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.8648788284640707E-2</v>
+        <v>5.8874360547273935E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3187679211786128E-2</v>
+        <v>3.3315324131831456E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.6306193927005755E-2</v>
+        <v>2.6407371595955773E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.2122923925513366E-2</v>
+        <v>1.216955055599611E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6907477389558064E-2</v>
+        <v>1.6972506148748671E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.5211804458569135E-3</v>
+        <v>-3.5347234475717475E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.3803911179033088E-2</v>
+        <v>4.3972387760490901E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3451851614573142E-2</v>
+        <v>2.3542051043859959E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12685611143513409</v>
+        <v>0.12734401955603844</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14735,43 +14735,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.472891297925623E-2</v>
+        <v>9.5093254952253375E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.06402033826488E-2</v>
+        <v>7.0911896472582073E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2812953280840855E-2</v>
+        <v>6.3054541562690247E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6117912017111869E-2</v>
+        <v>1.6179903986408454E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5837939191723077E-2</v>
+        <v>1.5898854342460474E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2412005755804451E-3</v>
+        <v>1.2459744239480622E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4593024401199067E-3</v>
+        <v>3.4726074495049831E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1215050405484024E-2</v>
+        <v>2.1296646753197424E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6886543323623417E-2</v>
+        <v>5.710533772102197E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1477620322824251</v>
+        <v>0.14833034779120366</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.22</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13731567198142991</v>
+        <v>0.13882089762469163</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5663AF8C-82FC-4290-A0E0-F1DCBEC6FF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3847BED3-1C4E-4EE3-B9FF-05315335850A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22991.044959999999</v>
+        <v>23167.899152000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13882089762469163</v>
+        <v>0.13581828655717021</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.4230787850279681E-2</v>
+        <v>4.3893148248369145E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.865384615384615E-2</v>
+        <v>3.8358778625954194E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13479,16 +13479,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.865384615384615E-2</v>
+        <v>3.8358778625954194E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.865384615384615E-2</v>
+        <v>3.8358778625954194E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8269230769230765E-2</v>
+        <v>2.8053435114503814E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14678,50 +14678,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.4230787850279681E-2</v>
+        <v>4.3893148248369145E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.2102634727611281E-2</v>
+        <v>6.1628568813660051E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.8874360547273935E-2</v>
+        <v>5.8424937947676427E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3315324131831456E-2</v>
+        <v>3.3061008680443427E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.6407371595955773E-2</v>
+        <v>2.620578860667367E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.216955055599611E-2</v>
+        <v>1.2076653223507589E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6972506148748671E-2</v>
+        <v>1.6842945033109367E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.5347234475717475E-3</v>
+        <v>-3.5077408258345588E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.3972387760490901E-2</v>
+        <v>4.3636720678349748E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3542051043859959E-2</v>
+        <v>2.3362340730548051E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12734401955603844</v>
+        <v>0.12637192780370227</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14735,43 +14735,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5093254952253375E-2</v>
+        <v>9.4367352242694186E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0911896472582073E-2</v>
+        <v>7.0370584285768464E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3054541562690247E-2</v>
+        <v>6.2573209184349096E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6179903986408454E-2</v>
+        <v>1.6056393268954954E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5898854342460474E-2</v>
+        <v>1.5777489042136349E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2459744239480622E-3</v>
+        <v>1.2364631688034206E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4726074495049831E-3</v>
+        <v>3.446098995691968E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1296646753197424E-2</v>
+        <v>2.1134076930653931E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.710533772102197E-2</v>
+        <v>5.666941911246455E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14833034779120366</v>
+        <v>0.1471980550599731</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.2</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13882089762469163</v>
+        <v>0.13581828655717021</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3847BED3-1C4E-4EE3-B9FF-05315335850A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB1C097-FAB2-4A87-8DBF-FD9B35D19E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23167.899152000002</v>
+        <v>23300.539796000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13581828655717021</v>
+        <v>0.13358675397086195</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.3893148248369145E-2</v>
+        <v>4.3643282129308222E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8358778625954194E-2</v>
+        <v>3.8140417457305502E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13479,16 +13479,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8358778625954194E-2</v>
+        <v>3.8140417457305502E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8358778625954194E-2</v>
+        <v>3.8140417457305502E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.8053435114503814E-2</v>
+        <v>2.7893738140417457E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14678,50 +14678,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3893148248369145E-2</v>
+        <v>4.3643282129308222E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.1628568813660051E-2</v>
+        <v>6.1277742046219864E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.8424937947676427E-2</v>
+        <v>5.8092348168088143E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3061008680443427E-2</v>
+        <v>3.2872805594976011E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.620578860667367E-2</v>
+        <v>2.6056609544396592E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.2076653223507589E-2</v>
+        <v>1.2007905671950621E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6842945033109367E-2</v>
+        <v>1.6747064890605901E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-3.5077408258345588E-3</v>
+        <v>-3.4877726617406242E-3</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>4.3636720678349748E-2</v>
+        <v>4.3388314298776605E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.3362340730548051E-2</v>
+        <v>2.32293482785715E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.12637192780370227</v>
+        <v>0.1256525430154459</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14735,43 +14735,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4367352242694186E-2</v>
+        <v>9.3830156689130459E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0370584285768464E-2</v>
+        <v>6.9969992724369406E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2573209184349096E-2</v>
+        <v>6.2217004957493216E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6056393268954954E-2</v>
+        <v>1.5964990650725611E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5777489042136349E-2</v>
+        <v>1.5687674114002743E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2364631688034206E-3</v>
+        <v>1.2294244790379363E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.446098995691968E-3</v>
+        <v>3.4264817338569096E-3</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1134076930653931E-2</v>
+        <v>2.1013769092339013E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.666941911246455E-2</v>
+        <v>5.6346822798731357E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1471980550599731</v>
+        <v>0.14636011546760133</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.24</v>
+        <v>-5.27</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13581828655717021</v>
+        <v>0.13358675397086195</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB1C097-FAB2-4A87-8DBF-FD9B35D19E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B233F4E1-B1E4-4480-AD72-180ECCA62FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2445,6 +2434,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
@@ -2470,9 +2471,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3149,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3894,6 +3892,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4223,10 +4225,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4238,18 +4240,18 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4263,7 +4265,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4272,10 +4274,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4289,7 +4291,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4299,7 +4301,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4312,20 +4314,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4341,17 +4343,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4365,7 +4367,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4391,35 +4393,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4427,7 +4429,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4437,26 +4439,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4477,11 +4479,11 @@
         <v>6.9895661568976033</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13358675397086195</v>
+        <v>0.13009220438153313</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4490,7 +4492,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4501,7 +4503,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4509,37 +4511,37 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>3.2714103607293628</v>
+        <v>3.2367222690014161</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>4.6114224254647684</v>
+        <v>4.5682049056603367</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F30" s="312">
         <v>0.187</v>
@@ -4547,18 +4549,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>6.4058499272029952</v>
+        <v>6.3521223870188166</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F31" s="312">
         <v>0.06</v>
@@ -4566,18 +4568,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>5.9535611226219638</v>
+        <v>5.902408832447132</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4589,7 +4591,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4597,45 +4599,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4650,18 +4652,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4674,7 +4676,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4686,17 +4688,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4708,17 +4710,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4733,7 +4735,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4748,7 +4750,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4761,12 +4763,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4778,17 +4780,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4800,17 +4802,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4821,27 +4823,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4854,7 +4856,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4867,24 +4869,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>4.3643282129308222E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
-        <v>3.8140417457305502E-2</v>
+        <f>Normalized_FCF!C94</f>
+        <v>3.4326375711574951E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4893,73 +4895,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>450</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>4.9029562887232557E-2</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>6.8755155989910458E-2</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>5.0475725130946753E-2</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>6.490075699179193E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.56944999111533989</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.62106298336522048</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.7057676125178334</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.7057676125178334</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4970,33 +4972,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5005,7 +5007,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5014,7 +5016,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5026,31 +5028,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5058,7 +5060,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5071,7 +5073,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5083,36 +5085,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5125,7 +5127,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5138,7 +5140,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5147,7 +5149,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5156,12 +5158,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5174,7 +5176,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5187,7 +5189,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5200,12 +5202,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5218,7 +5220,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5229,18 +5231,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+    <row r="116" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5253,7 +5255,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5266,7 +5268,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5274,30 +5276,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+    <row r="123" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5412,7 +5414,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5423,18 +5425,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+    <row r="134" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5443,31 +5445,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5476,20 +5478,20 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.20099999999999998</v>
+        <v>0.18089999999999998</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5498,7 +5500,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5511,11 +5513,11 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5525,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.34688091727946951</v>
+        <v>0.3121928255515225</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5540,11 +5542,11 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>3.2714103607293628</v>
+        <v>3.2367222690014161</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5553,7 +5555,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5566,21 +5568,21 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53195802324569241</v>
+        <v>0.53692086227593971</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5594,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.43217519804432247</v>
+        <v>0.38895767823989019</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5609,11 +5611,11 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>4.6114224254647684</v>
+        <v>4.5682049056603367</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5622,7 +5624,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5635,21 +5637,21 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34024196610342983</v>
+        <v>0.34642511378875263</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5663,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.53727540184178957</v>
+        <v>0.4835478616576106</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5678,11 +5680,11 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>6.4058499272029952</v>
+        <v>6.3521223870188166</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5691,7 +5693,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5704,21 +5706,21 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>8.3512512306442965E-2</v>
+        <v>9.119933277256842E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5732,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.51152290174831927</v>
+        <v>0.46037061157348735</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5747,11 +5749,11 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>5.9535611226219638</v>
+        <v>5.902408832447132</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5760,7 +5762,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5773,16 +5775,16 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.14739695926290697</v>
+        <v>0.1547224233415424</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5791,98 +5793,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+    </row>
+    <row r="191" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5920,7 +5922,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -5944,12 +5946,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -6207,7 +6209,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6223,7 +6225,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6239,7 +6241,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6491,7 +6493,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>385024.86</v>
@@ -6527,7 +6529,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-310465.5</v>
@@ -6563,7 +6565,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-77562.899999999994</v>
@@ -6625,7 +6627,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6778,7 +6780,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7179,7 +7181,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7228,7 +7230,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7576,12 +7578,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7630,7 +7632,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7679,7 +7681,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7728,7 +7730,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7930,7 +7932,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8182,7 +8184,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8548,15 +8550,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8577,7 +8579,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8588,19 +8590,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8662,7 +8664,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8683,7 +8685,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>1010697.32</v>
@@ -8694,7 +8696,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8704,7 +8706,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8726,7 +8728,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8790,19 +8792,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8810,7 +8812,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8839,7 +8841,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8859,7 +8861,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>238829.19</v>
@@ -8870,7 +8872,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8879,7 +8881,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8900,7 +8902,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8920,7 +8922,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8940,7 +8942,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8999,16 +9001,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -9041,7 +9043,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>200865.76</v>
@@ -9085,7 +9087,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9135,10 +9137,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9146,10 +9148,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9171,7 +9173,7 @@
         <v>13000.4</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9187,7 +9189,7 @@
         <v>59651.54</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9203,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9232,14 +9234,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>72651.94</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9259,7 +9261,7 @@
         <v>80439.799999999988</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9278,7 +9280,7 @@
         <v>153091.74</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9302,13 +9304,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9316,7 +9318,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9348,7 +9350,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9375,7 +9377,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9389,7 +9391,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9401,7 +9403,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9415,7 +9417,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9432,7 +9434,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9469,10 +9471,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9481,7 +9483,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9492,12 +9494,12 @@
         <v>7.6472162169116883E-2</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9508,13 +9510,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9522,7 +9524,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9533,12 +9535,12 @@
         <v>381755.93838365644</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9548,7 +9550,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9558,7 +9560,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9568,7 +9570,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9581,7 +9583,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9593,7 +9595,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9604,12 +9606,12 @@
         <v>-224948.28161634356</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9620,12 +9622,12 @@
         <v>2.6970831501382762</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9633,12 +9635,12 @@
         <v>224948.28161634356</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9646,7 +9648,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9654,10 +9656,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9666,7 +9668,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9680,7 +9682,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9694,7 +9696,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9708,7 +9710,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9722,7 +9724,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9733,15 +9735,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>289</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9758,7 +9760,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9775,7 +9777,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9792,7 +9794,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9820,17 +9822,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Q809"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10152,7 +10154,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10319,7 +10321,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10431,7 +10433,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10541,7 +10543,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10598,7 +10600,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10663,7 +10665,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10688,7 +10690,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10782,7 +10784,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -11001,7 +11003,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -11016,7 +11018,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11076,7 +11078,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11193,14 +11195,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-29127.89</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11258,7 +11260,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11370,7 +11372,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11552,21 +11554,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11620,7 +11622,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11705,7 +11707,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11760,7 +11762,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11876,11 +11878,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11893,7 +11895,7 @@
         <v>2.0532393857421991E-2</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11920,7 +11922,7 @@
         <v>2.731090181487239E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11999,17 +12001,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12064,7 +12066,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12119,7 +12121,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12174,7 +12176,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12229,13 +12231,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12285,7 +12287,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12344,17 +12346,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12379,7 +12381,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12404,7 +12406,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12429,7 +12431,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12459,12 +12461,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>464</v>
+        <v>59</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12482,7 +12484,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12674,7 +12676,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12847,7 +12849,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12961,7 +12963,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13133,7 +13135,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13240,7 +13242,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13301,7 +13303,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13420,7 +13422,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13475,1310 +13477,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
-        <v>3.8140417457305502E-2</v>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0.1</v>
       </c>
       <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8140417457305502E-2</v>
-      </c>
-      <c r="H93" s="23">
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
+        <v>3.4326375711574951E-2</v>
+      </c>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>3.4326375711574951E-2</v>
+      </c>
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.7893738140417457E-2</v>
-      </c>
-      <c r="I93" s="23">
+        <v>2.5104364326375715E-2</v>
+      </c>
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="J93" s="23">
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>-8.3104280294111876E-2</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-2.5937195218365683E-2</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>4.7470935229053657E-2</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.48308434654268462</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.1082097484341995</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.21428262970296608</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.33100190389533934</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>7.798889056610836E-2</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.14502935395370053</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.25984147979682559</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-0.28689620172736641</v>
+        <f>C4/G4-1</f>
+        <v>-8.3104280294111876E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>-2.5937195218365683E-2</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>4.7470935229053657E-2</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.48308434654268462</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.1082097484341995</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.21428262970296608</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.33100190389533934</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>7.798889056610836E-2</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.14502935395370053</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.25984147979682559</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-0.28689620172736641</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>0.18179194962258727</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>0.52506923477535028</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>0.33192526994236915</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>0.77622734281400874</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>-0.20156018551932486</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>-18.699353793916568</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>-1.0281031647648389</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>0.3574558457445296</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>-0.76043969306449644</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>4823088.2699999996</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>4823088.2699999996</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>4325166.3499999996</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>4263867.49</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>3465426.38</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>3328189.6169999996</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>3185654.2935000001</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>3014920.057</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>2839595.6228</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>2981119.801</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>3144283.1915000002</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>779805.94000000006</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>614740.03</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>627070.1</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>565721.97</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>737082.00840000005</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>483752.78779999999</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>75410.259999999995</v>
+        <f>BS!C4</f>
+        <v>779805.94000000006</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>614740.03</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>627070.1</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>565721.97</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>737082.00840000005</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>483752.78779999999</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="346">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="346">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>75410.259999999995</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>98279.37</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>130107.73</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>115109.66</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>101122.2853</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>512937.82659999997</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346">
+      <c r="N104" s="346">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="346">
+      <c r="O104" s="346">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="346">
+      <c r="P104" s="346">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>1995570.48</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>1995570.48</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>1647330.89</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>1695609.48</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>1189596.92</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>1061667.9129999999</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>918370.71239999996</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>724476.08160000003</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>526758.79269999999</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>664276.83160000003</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>845128.23759999999</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>2827517.7899999996</v>
+        <f>BS!G30</f>
+        <v>1995570.48</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>1995570.48</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>1647330.89</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>1695609.48</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>1189596.92</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>1061667.9129999999</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>918370.71239999996</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>724476.08160000003</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>526758.79269999999</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>664276.83160000003</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>845128.23759999999</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>2827517.7899999996</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>2827517.7899999996</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>2677835.46</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>2568258.0099999998</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>2275829.46</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>2266521.7039999999</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>2267283.5811000001</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>2290443.9753999999</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>2312836.8300999999</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>2316842.9693999998</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>2299154.9539000001</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>0.28392637537503096</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>0.20522517683277544</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.20391172454833276</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.19269530384629718</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.37234861883529258</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.27081915809764734</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>2.7456782116700319E-2</v>
+        <v>0.28392637537503096</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>3.2809643268657429E-2</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>0.20522517683277544</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>4.2308653532306596E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.20391172454833276</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>3.9208466500503705E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.19269530384629718</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>5.1083519657001315E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.37234861883529258</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.28715780840870436</v>
+        <f t="shared" si="43"/>
+        <v>0.27081915809764734</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
+        <f>C104/C$4</f>
+        <v>2.7456782116700319E-2</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>3.2809643268657429E-2</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>4.2308653532306596E-2</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>3.9208466500503705E-2</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>5.1083519657001315E-2</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.28715780840870436</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>1.7610851206468958</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>3.1434722210465975</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>2.2856524892428709</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>8.1539714870902102</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>5.5283768180985335</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>-2.6114096803023532</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>4.7151896080097524</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>1.0852517198711884</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>2.5043513481233903</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>1.06315880040684</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>1.7610851206468958</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>3.1434722210465975</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>2.2856524892428709</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>8.1539714870902102</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>5.5283768180985335</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>-2.6114096803023532</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>4.7151896080097524</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>1.0852517198711884</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>2.5043513481233903</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>1.06315880040684</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>2.6966217633893392</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>3.7861910453244887</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>4.3259603091518297</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>4.9959714956726939</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>7.2225229170749161</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>-0.19170708459852326</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>-4.6323291769407335</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.52560763000373034</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>6.074739590031685</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>1.2383676530033612</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>5.0475725130946753E-2</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>6.490075699179193E-2</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>5.3492844834545535E-2</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>3.6740758340166678E-2</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>4.0910436046285456E-2</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>2.5524516454836912E-2</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>3.88181756477603E-2</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>-2.9191498341973993E-3</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>0.11197354879760087</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>7.0524649222070246E-2</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>0.21789678212471589</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.56944999111533989</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.62106298336522048</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.71100242190684759</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.68853847754072672</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.57122786720403518</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.5367054875647731</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.4617699528795402</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.36658090327600346</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>0.36105623968705886</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>0.40225432231799124</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>0.51526868771864565</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.7057676125178334</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.7057676125178334</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.6151725580629961</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>1.6602177325634042</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>1.5227091664416716</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>1.4684128597252557</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>1.4050533069861695</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.3163037775126016</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>1.2277544121766795</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>1.2867163810294964</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>1.3675821136659057</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>4.9029562887232557E-2</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>6.8755155989910458E-2</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>6.1430733699135709E-2</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>4.1999234920011404E-2</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>3.5584466317526542E-2</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>2.0116005162062175E-2</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>2.518567486263517E-2</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>-1.4085827049602441E-3</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>4.9636574316847225E-2</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>3.6502657546057825E-2</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>0.1535458137787413</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (CNY)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.23000009682145431</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.32293370058357868</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.30614667484582447</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.17323968548552357</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.13731833229897003</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>6.3281662891179771E-2</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>8.8257031973493091E-2</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>-1.8380561927373088E-2</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.22865641635455269</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.1224186654280718</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.66218890169139988</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3643282129308222E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (CNY)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>0.23000009682145431</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.32293370058357868</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.30614667484582447</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.17323968548552357</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.13731833229897003</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>6.3281662891179771E-2</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>8.8257031973493091E-2</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>-1.8380561927373088E-2</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.22865641635455269</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.1224186654280718</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.66218890169139988</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>4.3643282129308222E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>6.1277742046219864E-2</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>5.8092348168088143E-2</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>3.2872805594976011E-2</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>2.6056609544396592E-2</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>1.2007905671950621E-2</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>1.6747064890605901E-2</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>-3.4877726617406242E-3</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>4.3388314298776605E-2</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>2.32293482785715E-2</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>0.1256525430154459</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>9.3830156689130459E-2</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>6.9969992724369406E-2</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>6.2217004957493216E-2</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.5964990650725611E-2</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.5687674114002743E-2</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.2294244790379363E-3</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>3.4264817338569096E-3</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.1013769092339013E-2</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.6346822798731357E-2</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.14636011546760133</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15460,6 +15482,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15481,13 +15504,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15504,20 +15527,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>10000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15528,7 +15551,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15538,7 +15561,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15547,9 +15570,9 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15559,15 +15582,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15577,13 +15600,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15593,13 +15616,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15609,13 +15632,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15629,7 +15652,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15660,7 +15683,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15670,13 +15693,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15684,9 +15707,9 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15694,7 +15717,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15719,7 +15742,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -16491,7 +16514,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16528,7 +16551,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16749,7 +16772,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16978,19 +17001,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17115,7 +17138,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17241,18 +17264,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17264,31 +17287,31 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>10000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
-        <v>88869.231480000002</v>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
+        <v>79982.308332000001</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17298,7 +17321,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17307,29 +17330,29 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1481153.858</v>
+        <v>1333038.4722</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.35</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17342,7 +17365,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17352,13 +17375,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1">
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17366,9 +17389,9 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1">
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17376,13 +17399,13 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1">
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>4.0095282229211753</v>
+        <v>3.6085754006290576</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17398,16 +17421,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17417,7 +17440,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>94321.427867599763</v>
+        <v>84889.285080839778</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17429,7 +17452,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>88982.479120377131</v>
+        <v>80084.231208339406</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17439,7 +17462,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>100108.12073900951</v>
+        <v>90097.308665108547</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17451,7 +17474,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>89095.87107423415</v>
+        <v>80186.283966810734</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17461,7 +17484,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>106249.83171335794</v>
+        <v>95624.84854202214</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17473,7 +17496,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>89209.407525472299</v>
+        <v>80288.466772925065</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17483,7 +17506,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>112768.34142704915</v>
+        <v>101491.50728434422</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17495,7 +17518,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>89323.088658227178</v>
+        <v>80390.779792404443</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17505,7 +17528,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>119686.76677545041</v>
+        <v>107718.09009790535</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17517,7 +17540,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>89436.914656868961</v>
+        <v>80493.223191182056</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17527,7 +17550,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>127029.64289341778</v>
+        <v>114326.67860407599</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -17539,7 +17562,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>89550.885706002882</v>
+        <v>80595.797135402579</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -17549,7 +17572,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>134823.01016539024</v>
+        <v>121340.70914885121</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -17561,7 +17584,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>89665.001990469304</v>
+        <v>80698.501791422357</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -17571,7 +17594,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>143094.50657362121</v>
+        <v>128785.05591625907</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -17583,7 +17606,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>89779.263695344256</v>
+        <v>80801.337325809815</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -17593,7 +17616,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>151873.46571204523</v>
+        <v>136686.11914084069</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -17605,7 +17628,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>89893.671005939497</v>
+        <v>80904.303905345543</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -17615,7 +17638,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>161191.02081337204</v>
+        <v>145071.91873203483</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -17627,7 +17650,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>90008.224107803006</v>
+        <v>81007.401697022695</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18073,11 +18096,11 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>1572023.7977933295</v>
+        <v>1414821.4180139964</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18089,7 +18112,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>877809.87787406251</v>
+        <v>790028.8900866562</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18100,7 +18123,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>1772754.6854148009</v>
+        <v>1595479.2168733208</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18110,7 +18133,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18121,7 +18144,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>1772754.6854148009</v>
+        <v>1595479.2168733208</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18151,19 +18174,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>1481153.8579999995</v>
+        <v>1333038.4721999995</v>
       </c>
       <c r="C51" s="123">
-        <v>1503156.7314593862</v>
+        <v>1352841.0583134475</v>
       </c>
       <c r="D51" s="123">
-        <v>1594071.9362737308</v>
+        <v>1434664.7426463575</v>
       </c>
       <c r="E51" s="123">
-        <v>1665488.2665475446</v>
+        <v>1498939.4398927903</v>
       </c>
       <c r="F51" s="123">
-        <v>1714737.9594915695</v>
+        <v>1543264.1635424129</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18172,19 +18195,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>1481153.8579999993</v>
+        <v>1333038.4721999993</v>
       </c>
       <c r="C52" s="123">
-        <v>1523216.6600429146</v>
+        <v>1370894.9940386233</v>
       </c>
       <c r="D52" s="123">
-        <v>1712283.6663535989</v>
+        <v>1541055.2997182389</v>
       </c>
       <c r="E52" s="123">
-        <v>1879571.6143575252</v>
+        <v>1691614.4529217728</v>
       </c>
       <c r="F52" s="123">
-        <v>2005456.3362036608</v>
+        <v>1804910.7025832951</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18193,19 +18216,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>1481153.8579999991</v>
+        <v>1333038.472199999</v>
       </c>
       <c r="C53" s="123">
-        <v>1549740.7490917698</v>
+        <v>1394766.6741825927</v>
       </c>
       <c r="D53" s="123">
-        <v>1885663.6826576078</v>
+        <v>1697097.314391847</v>
       </c>
       <c r="E53" s="123">
-        <v>2220582.538817998</v>
+        <v>1998524.2849361985</v>
       </c>
       <c r="F53" s="123">
-        <v>2495705.8742629169</v>
+        <v>2246135.2868366255</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18214,19 +18237,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>1481153.8579999991</v>
+        <v>1333038.4721999993</v>
       </c>
       <c r="C54" s="123">
-        <v>1578619.7291378824</v>
+        <v>1420757.756224094</v>
       </c>
       <c r="D54" s="123">
-        <v>2096332.0586760258</v>
+        <v>1886698.8528084233</v>
       </c>
       <c r="E54" s="123">
-        <v>2674176.7016024138</v>
+        <v>2406759.0314421728</v>
       </c>
       <c r="F54" s="123">
-        <v>3190604.7270988859</v>
+        <v>2871544.2543889983</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18235,19 +18258,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>1481153.8579999986</v>
+        <v>1333038.472199999</v>
       </c>
       <c r="C55" s="123">
-        <v>1607314.2183029864</v>
+        <v>1446582.7964726875</v>
       </c>
       <c r="D55" s="123">
-        <v>2331110.0908885882</v>
+        <v>2097999.0817997293</v>
       </c>
       <c r="E55" s="123">
-        <v>3231372.6865231837</v>
+        <v>2908235.4178708652</v>
       </c>
       <c r="F55" s="123">
-        <v>4105279.6531012338</v>
+        <v>3694751.6877911109</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18256,19 +18279,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>1481153.8579999988</v>
+        <v>1333038.4721999988</v>
       </c>
       <c r="C56" s="123">
-        <v>1634343.9155179767</v>
+        <v>1470909.523966179</v>
       </c>
       <c r="D56" s="123">
-        <v>2580323.6685524788</v>
+        <v>2322291.3016972309</v>
       </c>
       <c r="E56" s="123">
-        <v>3887366.7839434934</v>
+        <v>3498630.1055491441</v>
       </c>
       <c r="F56" s="123">
-        <v>5264636.039729842</v>
+        <v>4738172.4357568584</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18281,7 +18304,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18318,23 +18341,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>3.35</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>3.35</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>3.35</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>3.35</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>3.35</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18345,23 +18368,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.3499999999999992</v>
+        <v>3.0149999999999992</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>3.3997650029339113</v>
+        <v>3.0597885026405196</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>3.6053924834843176</v>
+        <v>3.2448532351358854</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>3.7669183810979039</v>
+        <v>3.3902265429881138</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>3.878308882814764</v>
+        <v>3.4904779945332884</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18372,23 +18395,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>3.3499999999999983</v>
+        <v>3.0149999999999983</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>3.4451355499515999</v>
+        <v>3.1006219949564402</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>3.8727578848763708</v>
+        <v>3.4854820963887332</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>4.2511214308282277</v>
+        <v>3.8260092877454053</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>4.5358412227031879</v>
+        <v>4.0822571004328703</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18399,23 +18422,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>3.3499999999999979</v>
+        <v>3.0149999999999979</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>3.5051264130437345</v>
+        <v>3.1546137717393608</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>4.2649001673821969</v>
+        <v>3.8384101506439769</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0224029494715019</v>
+        <v>4.5201626545243521</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>5.6446632020187941</v>
+        <v>5.0801968818169163</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18426,23 +18449,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>3.3499999999999979</v>
+        <v>3.0149999999999983</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>3.5704434512649432</v>
+        <v>3.2133991061384486</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>4.7413794040596464</v>
+        <v>4.2672414636536828</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.0483196272835054</v>
+        <v>5.4434876645551551</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>7.2163508051850664</v>
+        <v>6.4947157246665617</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18453,23 +18476,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>3.349999999999997</v>
+        <v>3.0149999999999979</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>3.6353432172034381</v>
+        <v>3.2718088954830935</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.2723886598935428</v>
+        <v>4.7451497939041882</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>7.3085577446152561</v>
+        <v>6.57770197015373</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>9.2851169806622025</v>
+        <v>8.356605282595984</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18479,40 +18502,40 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>3.3499999999999974</v>
+        <v>3.0149999999999975</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>3.6964776396546521</v>
+        <v>3.3268298756891865</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>5.8360475132022396</v>
+        <v>5.2524427618820164</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>8.7922525103470388</v>
+        <v>7.9130272593123356</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>11.90729149293751</v>
+        <v>10.716562343643758</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18530,7 +18553,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.6446632020187941</v>
+        <v>5.0801968818169163</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18552,7 +18575,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>4.2511214308282277</v>
+        <v>3.8260092877454053</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18575,7 +18598,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>3.8727578848763708</v>
+        <v>3.4854820963887332</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18598,7 +18621,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>3.4451355499515999</v>
+        <v>3.1006219949564402</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18621,7 +18644,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>3.3499999999999979</v>
+        <v>3.0149999999999979</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18637,7 +18660,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18689,32 +18712,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="6" width="42.6640625" customWidth="1"/>
-    <col min="8" max="9" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="6" width="42.73046875" customWidth="1"/>
+    <col min="8" max="9" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18726,14 +18749,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18741,7 +18764,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.20099999999999998</v>
+        <v>0.18089999999999998</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18750,7 +18773,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.20099999999999998</v>
+        <v>0.18089999999999998</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18762,7 +18785,7 @@
         <v>10000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18770,12 +18793,12 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>7.1905661568976029</v>
+        <v>7.1704661568976036</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18785,11 +18808,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 海油工程(600583.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18810,8 +18833,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18832,8 +18855,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18843,8 +18866,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18855,10 +18878,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>447</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>444</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18869,15 +18892,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.14806091180696912</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18888,14 +18911,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.32719702788845018</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18912,12 +18935,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.32982639766138688</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18926,38 +18949,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18967,12 +18990,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18982,44 +19005,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.05</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19029,55 +19052,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19087,55 +19110,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.08</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19145,24 +19168,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19175,7 +19198,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19184,12 +19207,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>15</v>
@@ -19204,39 +19227,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19246,55 +19269,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.1</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19304,23 +19327,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.1</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19331,7 +19354,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19340,7 +19363,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19349,15 +19372,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19365,19 +19388,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
         <v>6.1350776830187602E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19393,20 +19416,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19416,19 +19439,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19438,14 +19461,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19454,7 +19477,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19463,12 +19486,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19478,11 +19501,11 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
-        <v>0.20099999999999998</v>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
+        <v>0.18089999999999998</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19491,25 +19514,25 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.34688091727946951</v>
+        <v>0.3121928255515225</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19517,7 +19540,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19531,18 +19554,18 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>3.2714103607293628</v>
+        <v>3.2367222690014161</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53195802324569241</v>
+        <v>0.53692086227593971</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19550,12 +19573,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19568,11 +19591,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13358675397086195</v>
+        <v>0.13009220438153313</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19580,12 +19603,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19594,11 +19617,11 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.43217519804432247</v>
+        <v>0.38895767823989019</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19606,7 +19629,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19620,30 +19643,30 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>4.6114224254647684</v>
+        <v>4.5682049056603367</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.34024196610342983</v>
+        <v>0.34642511378875263</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19654,11 +19677,11 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.53727540184178957</v>
+        <v>0.4835478616576106</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19666,7 +19689,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19678,21 +19701,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>6.4058499272029952</v>
+        <v>6.3521223870188166</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>8.3512512306442965E-2</v>
+        <v>9.119933277256842E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19700,12 +19723,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19714,17 +19737,17 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.51152290174831927</v>
+        <v>0.46037061157348735</v>
       </c>
       <c r="D103" s="116"/>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19734,21 +19757,21 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>5.9535611226219638</v>
+        <v>5.902408832447132</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.14739695926290697</v>
+        <v>0.1547224233415424</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19756,32 +19779,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
+        <v>322</v>
+      </c>
+      <c r="F110" s="284" t="s">
         <v>325</v>
-      </c>
-      <c r="F110" s="284" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B233F4E1-B1E4-4480-AD72-180ECCA62FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51AA909F-7B1E-4743-A14A-E988E1A7634D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23300.539796000001</v>
+        <v>23388.966892</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13009220438153313</v>
+        <v>0.12862338772690407</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.3643282129308222E-2</v>
+        <v>4.3478279172297601E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.4326375711574951E-2</v>
+        <v>3.4196597353497157E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.3121928255515225</v>
+        <v>0.31219282555152256</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4326375711574951E-2</v>
+        <v>3.4196597353497157E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4326375711574951E-2</v>
+        <v>3.4196597353497157E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5104364326375715E-2</v>
+        <v>2.5009451795841211E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3643282129308222E-2</v>
+        <v>4.3478279172297601E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.1277742046219864E-2</v>
+        <v>6.1046068163247383E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.8092348168088143E-2</v>
+        <v>5.7872717362159633E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.2872805594976011E-2</v>
+        <v>3.2748522776091409E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.6056609544396592E-2</v>
+        <v>2.5958096842905488E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.2007905671950621E-2</v>
+        <v>1.1962507162793908E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.6747064890605901E-2</v>
+        <v>1.6683748955291698E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.4877726617406242E-3</v>
+        <v>-3.4745863756848938E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.3388314298776605E-2</v>
+        <v>4.3224275303318092E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.32293482785715E-2</v>
+        <v>2.3141524655590131E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.1256525430154459</v>
+        <v>0.12517748614204158</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3830156689130459E-2</v>
+        <v>9.3475411295220703E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9969992724369406E-2</v>
+        <v>6.9705455889872731E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2217004957493216E-2</v>
+        <v>6.198177998600931E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5964990650725611E-2</v>
+        <v>1.5904631517830618E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5687674114002743E-2</v>
+        <v>1.562836343682315E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2294244790379363E-3</v>
+        <v>1.2247763713667153E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4264817338569096E-3</v>
+        <v>3.4135271715360896E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1013769092339013E-2</v>
+        <v>2.093432195021297E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6346822798731357E-2</v>
+        <v>5.6133791332573582E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14636011546760133</v>
+        <v>0.14580676909532306</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.27</v>
+        <v>-5.29</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.3121928255515225</v>
+        <v>0.31219282555152256</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13009220438153313</v>
+        <v>0.12862338772690407</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51AA909F-7B1E-4743-A14A-E988E1A7634D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF6327B-3418-437F-AA3F-7C1E757E08E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23388.966892</v>
+        <v>23875.315920000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12862338772690407</v>
+        <v>0.12067775792295632</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.3478279172297601E-2</v>
+        <v>4.2592610522491539E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.4196597353497157E-2</v>
+        <v>3.3499999999999995E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4196597353497157E-2</v>
+        <v>3.3499999999999995E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4196597353497157E-2</v>
+        <v>3.3499999999999995E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5009451795841211E-2</v>
+        <v>2.4499999999999997E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3478279172297601E-2</v>
+        <v>4.2592610522491539E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.1046068163247383E-2</v>
+        <v>5.9802537145107158E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.7872717362159633E-2</v>
+        <v>5.6693828675152678E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.2748522776091409E-2</v>
+        <v>3.2081423238059917E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.5958096842905488E-2</v>
+        <v>2.5429320796105558E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1962507162793908E-2</v>
+        <v>1.1718826461329587E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.6683748955291698E-2</v>
+        <v>1.6343894809906126E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.4745863756848938E-3</v>
+        <v>-3.4038077643283493E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.3224275303318092E-2</v>
+        <v>4.2343780806398647E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.3141524655590131E-2</v>
+        <v>2.2670123227420701E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.12517748614204158</v>
+        <v>0.12262757438729627</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3475411295220703E-2</v>
+        <v>9.1571282546614355E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9705455889872731E-2</v>
+        <v>6.8285529936560507E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.198177998600931E-2</v>
+        <v>6.0719188171479491E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5904631517830618E-2</v>
+        <v>1.5580648283208142E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.562836343682315E-2</v>
+        <v>1.5310007885332308E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2247763713667153E-3</v>
+        <v>1.199827223061097E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4135271715360896E-3</v>
+        <v>3.3439923587825766E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.093432195021297E-2</v>
+        <v>2.0507882058634557E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6133791332573582E-2</v>
+        <v>5.4990325212835971E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14580676909532306</v>
+        <v>0.14283663120634427</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.29</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12862338772690407</v>
+        <v>0.12067775792295632</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF6327B-3418-437F-AA3F-7C1E757E08E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6170AFB-4A08-466B-A52F-3984F14EE79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.4</v>
+        <v>5.43</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23875.315920000001</v>
+        <v>24007.956564</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12067775792295632</v>
+        <v>0.1185488785993456</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.2592610522491539E-2</v>
+        <v>4.2357292232312029E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.3499999999999995E-2</v>
+        <v>3.3314917127071818E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3499999999999995E-2</v>
+        <v>3.3314917127071818E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3499999999999995E-2</v>
+        <v>3.3314917127071818E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4499999999999997E-2</v>
+        <v>2.4364640883977901E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.2592610522491539E-2</v>
+        <v>4.2357292232312029E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.9802537145107158E-2</v>
+        <v>5.9472136387399392E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.6693828675152678E-2</v>
+        <v>5.6380603102361787E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.2081423238059917E-2</v>
+        <v>3.1904177805805449E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.5429320796105558E-2</v>
+        <v>2.5288827311044204E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1718826461329587E-2</v>
+        <v>1.1654081563753181E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.6343894809906126E-2</v>
+        <v>1.6253597048525432E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.4038077643283493E-3</v>
+        <v>-3.3850021965696297E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.2343780806398647E-2</v>
+        <v>4.2109837266031805E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2670123227420701E-2</v>
+        <v>2.2544873927821694E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.12262757438729627</v>
+        <v>0.12195007397631674</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1571282546614355E-2</v>
+        <v>9.1065363858511522E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8285529936560507E-2</v>
+        <v>6.7908261815364038E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0719188171479491E-2</v>
+        <v>6.038372304346027E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5580648283208142E-2</v>
+        <v>1.5494567353466659E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5310007885332308E-2</v>
+        <v>1.522542220640782E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.199827223061097E-3</v>
+        <v>1.1931983433756765E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3439923587825766E-3</v>
+        <v>3.3255172628777006E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0507882058634557E-2</v>
+        <v>2.0394578842840995E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4990325212835971E-2</v>
+        <v>5.4686511261383838E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14283663120634427</v>
+        <v>0.14204747854774569</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.4</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.4</v>
+        <v>5.43</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.4</v>
+        <v>5.43</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12067775792295632</v>
+        <v>0.1185488785993456</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6170AFB-4A08-466B-A52F-3984F14EE79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2B3137-4563-4FAA-B6A9-B67F04CEEADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.43</v>
+        <v>5.48</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24007.956564</v>
+        <v>24229.024303999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1185488785993456</v>
+        <v>0.11503604460416361</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.2357292232312029E-2</v>
+        <v>4.197082058785663E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.3314917127071818E-2</v>
+        <v>3.3010948905109486E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3314917127071818E-2</v>
+        <v>3.3010948905109486E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3314917127071818E-2</v>
+        <v>3.3010948905109486E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4364640883977901E-2</v>
+        <v>2.4142335766423356E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.2357292232312029E-2</v>
+        <v>4.197082058785663E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.9472136387399392E-2</v>
+        <v>5.8929507405762527E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.6380603102361787E-2</v>
+        <v>5.5866181541208842E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.1904177805805449E-2</v>
+        <v>3.1613081292978754E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.5288827311044204E-2</v>
+        <v>2.505808983557847E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1654081563753181E-2</v>
+        <v>1.154774870277003E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.6253597048525432E-2</v>
+        <v>1.610529780538195E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.3850021965696297E-3</v>
+        <v>-3.3541171400315851E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.2109837266031805E-2</v>
+        <v>4.1725623422363627E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2544873927821694E-2</v>
+        <v>2.2339172523370764E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.12195007397631674</v>
+        <v>0.1208373908195985</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1065363858511522E-2</v>
+        <v>9.0234475502138242E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7908261815364038E-2</v>
+        <v>6.7288660886391738E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.038372304346027E-2</v>
+        <v>5.9832776665326506E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5494567353466659E-2</v>
+        <v>1.5353193563745248E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.522542220640782E-2</v>
+        <v>1.5086504120582931E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1931983433756765E-3</v>
+        <v>1.1823114971769933E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3255172628777006E-3</v>
+        <v>3.2951749520850207E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0394578842840995E-2</v>
+        <v>2.0208496919092447E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4686511261383838E-2</v>
+        <v>5.4187546742575587E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14204747854774569</v>
+        <v>0.14075142491136114</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.43</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.43</v>
+        <v>5.48</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.43</v>
+        <v>5.48</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1185488785993456</v>
+        <v>0.11503604460416361</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2B3137-4563-4FAA-B6A9-B67F04CEEADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AA0376-BD29-4204-8350-03DC5D8368F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.48</v>
+        <v>5.53</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24229.024303999999</v>
+        <v>24450.092044000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11503604460416361</v>
+        <v>0.11156651152863062</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.197082058785663E-2</v>
+        <v>4.1591337580733148E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.3010948905109486E-2</v>
+        <v>3.2712477396021691E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3010948905109486E-2</v>
+        <v>3.2712477396021691E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3010948905109486E-2</v>
+        <v>3.2712477396021691E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4142335766423356E-2</v>
+        <v>2.3924050632911392E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.197082058785663E-2</v>
+        <v>4.1591337580733148E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8929507405762527E-2</v>
+        <v>5.839669088310645E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5866181541208842E-2</v>
+        <v>5.5361062359100266E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.1613081292978754E-2</v>
+        <v>3.1327248731559412E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.505808983557847E-2</v>
+        <v>2.4831524828023512E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.154774870277003E-2</v>
+        <v>1.1443338678332689E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.610529780538195E-2</v>
+        <v>1.595968028453763E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.3541171400315851E-3</v>
+        <v>-3.3237905836117697E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.1725623422363627E-2</v>
+        <v>4.1348357387803382E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2339172523370764E-2</v>
+        <v>2.2137190854985857E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.1208373908195985</v>
+        <v>0.11974482851562385</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0234475502138242E-2</v>
+        <v>8.9418612251666821E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7288660886391738E-2</v>
+        <v>6.6680264314182058E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9832776665326506E-2</v>
+        <v>5.9291793151173465E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5353193563745248E-2</v>
+        <v>1.52143762620839E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5086504120582931E-2</v>
+        <v>1.4950098115876033E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1823114971769933E-3</v>
+        <v>1.1716215198064961E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2951749520850207E-3</v>
+        <v>3.2653813268401291E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0208496919092447E-2</v>
+        <v>2.002577994875707E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4187546742575587E-2</v>
+        <v>5.3697605090291901E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14075142491136114</v>
+        <v>0.13947880804959475</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.48</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.48</v>
+        <v>5.53</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.48</v>
+        <v>5.53</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11503604460416361</v>
+        <v>0.11156651152863062</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AA0376-BD29-4204-8350-03DC5D8368F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32ABAC1-85FA-4771-9728-6149A401C375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.53</v>
+        <v>5.36</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24450.092044000001</v>
+        <v>23698.461727999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11156651152863062</v>
+        <v>0.12354140862530971</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.1591337580733148E-2</v>
+        <v>4.2910465824898193E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.2712477396021691E-2</v>
+        <v>3.3749999999999995E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2712477396021691E-2</v>
+        <v>3.3749999999999995E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2712477396021691E-2</v>
+        <v>3.3749999999999995E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.3924050632911392E-2</v>
+        <v>2.4682835820895522E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1591337580733148E-2</v>
+        <v>4.2910465824898193E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.839669088310645E-2</v>
+        <v>6.0248824735742286E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5361062359100266E-2</v>
+        <v>5.7116916948847844E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.1327248731559412E-2</v>
+        <v>3.2320836844314096E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.4831524828023512E-2</v>
+        <v>2.5619091846822765E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1443338678332689E-2</v>
+        <v>1.1806280390145479E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.595968028453763E-2</v>
+        <v>1.646586417415916E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.3237905836117697E-3</v>
+        <v>-3.4292093148084119E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.1348357387803382E-2</v>
+        <v>4.2659779170625502E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2137190854985857E-2</v>
+        <v>2.2839303251505932E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11974482851562385</v>
+        <v>0.12354270553944027</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9418612251666821E-2</v>
+        <v>9.2254650326812973E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6680264314182058E-2</v>
+        <v>6.8795123443549766E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9291793151173465E-2</v>
+        <v>6.1172316441415908E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.52143762620839E-2</v>
+        <v>1.5696921777858946E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4950098115876033E-2</v>
+        <v>1.5424261675521356E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1716215198064961E-3</v>
+        <v>1.2087811575615529E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2653813268401291E-3</v>
+        <v>3.368947525639163E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.002577994875707E-2</v>
+        <v>2.0660925954594515E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3697605090291901E-2</v>
+        <v>5.5400700774125788E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13947880804959475</v>
+        <v>0.14390257621534683</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.53</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.53</v>
+        <v>5.36</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.53</v>
+        <v>5.36</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11156651152863062</v>
+        <v>0.12354140862530971</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32ABAC1-85FA-4771-9728-6149A401C375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B71C8D-F8BE-41C2-BE6D-A308E8098F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.36</v>
+        <v>5.43</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23698.461727999998</v>
+        <v>24007.956564</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12354140862530971</v>
+        <v>0.1185488785993456</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.2910465824898193E-2</v>
+        <v>4.2357292232312029E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.3749999999999995E-2</v>
+        <v>3.3314917127071818E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3749999999999995E-2</v>
+        <v>3.3314917127071818E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3749999999999995E-2</v>
+        <v>3.3314917127071818E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4682835820895522E-2</v>
+        <v>2.4364640883977901E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.2910465824898193E-2</v>
+        <v>4.2357292232312029E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.0248824735742286E-2</v>
+        <v>5.9472136387399392E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.7116916948847844E-2</v>
+        <v>5.6380603102361787E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.2320836844314096E-2</v>
+        <v>3.1904177805805449E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.5619091846822765E-2</v>
+        <v>2.5288827311044204E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1806280390145479E-2</v>
+        <v>1.1654081563753181E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.646586417415916E-2</v>
+        <v>1.6253597048525432E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.4292093148084119E-3</v>
+        <v>-3.3850021965696297E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.2659779170625502E-2</v>
+        <v>4.2109837266031805E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2839303251505932E-2</v>
+        <v>2.2544873927821694E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.12354270553944027</v>
+        <v>0.12195007397631674</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2254650326812973E-2</v>
+        <v>9.1065363858511522E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8795123443549766E-2</v>
+        <v>6.7908261815364038E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1172316441415908E-2</v>
+        <v>6.038372304346027E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5696921777858946E-2</v>
+        <v>1.5494567353466659E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5424261675521356E-2</v>
+        <v>1.522542220640782E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2087811575615529E-3</v>
+        <v>1.1931983433756765E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.368947525639163E-3</v>
+        <v>3.3255172628777006E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0660925954594515E-2</v>
+        <v>2.0394578842840995E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5400700774125788E-2</v>
+        <v>5.4686511261383838E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14390257621534683</v>
+        <v>0.14204747854774569</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.36</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.36</v>
+        <v>5.43</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.36</v>
+        <v>5.43</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12354140862530971</v>
+        <v>0.1185488785993456</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B71C8D-F8BE-41C2-BE6D-A308E8098F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D75940-E160-465A-9431-A342040546A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.43</v>
+        <v>5.55</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24007.956564</v>
+        <v>24538.51914</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1185488785993456</v>
+        <v>0.11019061500170646</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.2357292232312029E-2</v>
+        <v>4.1441458886748529E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.3314917127071818E-2</v>
+        <v>3.2594594594594593E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3314917127071818E-2</v>
+        <v>3.2594594594594593E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3314917127071818E-2</v>
+        <v>3.2594594594594593E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4364640883977901E-2</v>
+        <v>2.3837837837837838E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.2357292232312029E-2</v>
+        <v>4.1441458886748529E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.9472136387399392E-2</v>
+        <v>5.8186252357401567E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.6380603102361787E-2</v>
+        <v>5.5161563035283689E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.1904177805805449E-2</v>
+        <v>3.1214357745139382E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.5288827311044204E-2</v>
+        <v>2.4742041855670277E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1654081563753181E-2</v>
+        <v>1.1402101421834194E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.6253597048525432E-2</v>
+        <v>1.5902167923151907E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.3850021965696297E-3</v>
+        <v>-3.311812959887043E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.2109837266031805E-2</v>
+        <v>4.1199354298117601E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2544873927821694E-2</v>
+        <v>2.205741719424717E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.12195007397631674</v>
+        <v>0.11931331562007205</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1065363858511522E-2</v>
+        <v>8.909638301832748E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7908261815364038E-2</v>
+        <v>6.6439975073410221E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.038372304346027E-2</v>
+        <v>5.9078129031709774E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5494567353466659E-2</v>
+        <v>1.5159549680959273E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.522542220640782E-2</v>
+        <v>1.4896223888431436E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1931983433756765E-3</v>
+        <v>1.1673994602756619E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3255172628777006E-3</v>
+        <v>3.2536141869235879E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0394578842840995E-2</v>
+        <v>1.9953614975968759E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4686511261383838E-2</v>
+        <v>5.3504100207083648E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14204747854774569</v>
+        <v>0.13897618171428092</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.43</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.43</v>
+        <v>5.55</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.43</v>
+        <v>5.55</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1185488785993456</v>
+        <v>0.11019061500170646</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D75940-E160-465A-9431-A342040546A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7DF901-0C2A-45F4-96F7-C1E578A3E405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24538.51914</v>
+        <v>24626.946236</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11019061500170646</v>
+        <v>0.10882144095987556</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.1441458886748529E-2</v>
+        <v>4.1292656520907418E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.2594594594594593E-2</v>
+        <v>3.2477558348294432E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2594594594594593E-2</v>
+        <v>3.2477558348294432E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2594594594594593E-2</v>
+        <v>3.2477558348294432E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.3837837837837838E-2</v>
+        <v>2.3752244165170557E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1441458886748529E-2</v>
+        <v>4.1292656520907418E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8186252357401567E-2</v>
+        <v>5.7977325059888452E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5161563035283689E-2</v>
+        <v>5.4963496381656096E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.1214357745139382E-2</v>
+        <v>3.1102277465982688E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.4742041855670277E-2</v>
+        <v>2.4653201489940758E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1402101421834194E-2</v>
+        <v>1.1361160303622938E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.5902167923151907E-2</v>
+        <v>1.5845068576928741E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.311812959887043E-3</v>
+        <v>-3.2999213514134807E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.1199354298117601E-2</v>
+        <v>4.1051421248573194E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.205741719424717E-2</v>
+        <v>2.1978216414375546E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11931331562007205</v>
+        <v>0.11888490156039494</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.909638301832748E-2</v>
+        <v>8.8776467818979812E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6439975073410221E-2</v>
+        <v>6.6201411428622403E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9078129031709774E-2</v>
+        <v>5.8865999304486404E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5159549680959273E-2</v>
+        <v>1.5105116827526743E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4896223888431436E-2</v>
+        <v>1.4842736549514266E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1673994602756619E-3</v>
+        <v>1.1632077207414586E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2536141869235879E-3</v>
+        <v>3.241931550704832E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9953614975968759E-2</v>
+        <v>1.9881968243559534E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3504100207083648E-2</v>
+        <v>5.3311984946016917E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13897618171428092</v>
+        <v>0.1384771649038167</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.55</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11019061500170646</v>
+        <v>0.10882144095987556</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7DF901-0C2A-45F4-96F7-C1E578A3E405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC61F5F-C973-452C-91C5-53122A9F6FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24626.946236</v>
+        <v>24538.51914</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10882144095987556</v>
+        <v>0.11019061500170646</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>3.2367222690014161</v>
+        <v>3.1476386351257846</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>4.5682049056603367</v>
+        <v>3.931774672331573</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4544,7 +4544,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.1292656520907418E-2</v>
+        <v>4.1441458886748529E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.2477558348294432E-2</v>
+        <v>3.2594594594594593E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.31219282555152256</v>
+        <v>0.3067846364883402</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>2.9245294434498934</v>
+        <v>2.8408539986374444</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>3.2367222690014161</v>
+        <v>3.1476386351257846</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53692086227593971</v>
+        <v>0.54966609307795733</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.38895767823989019</v>
+        <v>0.35311679999999995</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>4.1792472274204462</v>
+        <v>3.578657872331573</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>4.5682049056603367</v>
+        <v>3.931774672331573</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34642511378875263</v>
+        <v>0.43747943948544943</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2477558348294432E-2</v>
+        <v>3.2594594594594593E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2477558348294432E-2</v>
+        <v>3.2594594594594593E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.3752244165170557E-2</v>
+        <v>2.3837837837837838E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1292656520907418E-2</v>
+        <v>4.1441458886748529E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7977325059888452E-2</v>
+        <v>5.8186252357401567E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.4963496381656096E-2</v>
+        <v>5.5161563035283689E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.1102277465982688E-2</v>
+        <v>3.1214357745139382E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.4653201489940758E-2</v>
+        <v>2.4742041855670277E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1361160303622938E-2</v>
+        <v>1.1402101421834194E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.5845068576928741E-2</v>
+        <v>1.5902167923151907E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.2999213514134807E-3</v>
+        <v>-3.311812959887043E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.1051421248573194E-2</v>
+        <v>4.1199354298117601E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.1978216414375546E-2</v>
+        <v>2.205741719424717E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11888490156039494</v>
+        <v>0.11931331562007205</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8776467818979812E-2</v>
+        <v>8.909638301832748E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6201411428622403E-2</v>
+        <v>6.6439975073410221E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8865999304486404E-2</v>
+        <v>5.9078129031709774E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5105116827526743E-2</v>
+        <v>1.5159549680959273E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4842736549514266E-2</v>
+        <v>1.4896223888431436E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1632077207414586E-3</v>
+        <v>1.1673994602756619E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.241931550704832E-3</v>
+        <v>3.2536141869235879E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9881968243559534E-2</v>
+        <v>1.9953614975968759E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3311984946016917E-2</v>
+        <v>5.3504100207083648E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1384771649038167</v>
+        <v>0.13897618171428092</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.57</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.31219282555152256</v>
+        <v>0.3067846364883402</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>2.9245294434498934</v>
+        <v>2.8408539986374444</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>3.2367222690014161</v>
+        <v>3.1476386351257846</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19565,7 +19565,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53692086227593971</v>
+        <v>0.54966609307795733</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10882144095987556</v>
+        <v>0.11019061500170646</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.38895767823989019</v>
+        <v>0.35311679999999995</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>4.1792472274204462</v>
+        <v>3.578657872331573</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>4.5682049056603367</v>
+        <v>3.931774672331573</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19654,7 +19654,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.34642511378875263</v>
+        <v>0.43747943948544943</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC61F5F-C973-452C-91C5-53122A9F6FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4417AB-9792-4245-B57A-D4B629E00505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24538.51914</v>
+        <v>24317.451400000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11019061500170646</v>
+        <v>0.11364308755074815</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.1441458886748529E-2</v>
+        <v>4.1818199422082605E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.2594594594594593E-2</v>
+        <v>3.2890909090909089E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2594594594594593E-2</v>
+        <v>3.2890909090909089E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2594594594594593E-2</v>
+        <v>3.2890909090909089E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.3837837837837838E-2</v>
+        <v>2.4054545454545453E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1441458886748529E-2</v>
+        <v>4.1818199422082605E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8186252357401567E-2</v>
+        <v>5.8715218287923393E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5161563035283689E-2</v>
+        <v>5.5663031790149906E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.1214357745139382E-2</v>
+        <v>3.1498124633731556E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.4742041855670277E-2</v>
+        <v>2.4966969508903643E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1402101421834194E-2</v>
+        <v>1.1505756889305413E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.5902167923151907E-2</v>
+        <v>1.6046733086089653E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.311812959887043E-3</v>
+        <v>-3.3419203504314707E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.1199354298117601E-2</v>
+        <v>4.1573893882645943E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.205741719424717E-2</v>
+        <v>2.2257939168740328E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11931331562007205</v>
+        <v>0.12039798212570907</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.909638301832748E-2</v>
+        <v>8.9906350136675917E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6439975073410221E-2</v>
+        <v>6.7043974846804869E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9078129031709774E-2</v>
+        <v>5.9615202931998047E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5159549680959273E-2</v>
+        <v>1.5297363768967993E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4896223888431436E-2</v>
+        <v>1.5031644105598993E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1673994602756619E-3</v>
+        <v>1.1780121826418042E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2536141869235879E-3</v>
+        <v>3.2831924977138023E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9953614975968759E-2</v>
+        <v>2.0135011475750291E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3504100207083648E-2</v>
+        <v>5.399050111805713E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13897618171428092</v>
+        <v>0.1402396015480471</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.55</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11019061500170646</v>
+        <v>0.11364308755074815</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4417AB-9792-4245-B57A-D4B629E00505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E269B2-EFF1-4142-BACA-BA408E06B297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24317.451400000002</v>
+        <v>24450.092044000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11364308755074815</v>
+        <v>0.11156651152863062</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.1818199422082605E-2</v>
+        <v>4.1591337580733148E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.2890909090909089E-2</v>
+        <v>3.2712477396021691E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13502,16 +13502,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2890909090909089E-2</v>
+        <v>3.2712477396021691E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2890909090909089E-2</v>
+        <v>3.2712477396021691E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4054545454545453E-2</v>
+        <v>2.3924050632911392E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14701,50 +14701,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1818199422082605E-2</v>
+        <v>4.1591337580733148E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.8715218287923393E-2</v>
+        <v>5.839669088310645E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5663031790149906E-2</v>
+        <v>5.5361062359100266E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.1498124633731556E-2</v>
+        <v>3.1327248731559412E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.4966969508903643E-2</v>
+        <v>2.4831524828023512E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1505756889305413E-2</v>
+        <v>1.1443338678332689E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.6046733086089653E-2</v>
+        <v>1.595968028453763E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.3419203504314707E-3</v>
+        <v>-3.3237905836117697E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.1573893882645943E-2</v>
+        <v>4.1348357387803382E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2257939168740328E-2</v>
+        <v>2.2137190854985857E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.12039798212570907</v>
+        <v>0.11974482851562385</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14758,43 +14758,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9906350136675917E-2</v>
+        <v>8.9418612251666821E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7043974846804869E-2</v>
+        <v>6.6680264314182058E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9615202931998047E-2</v>
+        <v>5.9291793151173465E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5297363768967993E-2</v>
+        <v>1.52143762620839E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5031644105598993E-2</v>
+        <v>1.4950098115876033E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1780121826418042E-3</v>
+        <v>1.1716215198064961E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2831924977138023E-3</v>
+        <v>3.2653813268401291E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0135011475750291E-2</v>
+        <v>2.002577994875707E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.399050111805713E-2</v>
+        <v>5.3697605090291901E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1402396015480471</v>
+        <v>0.13947880804959475</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.5</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11364308755074815</v>
+        <v>0.11156651152863062</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E269B2-EFF1-4142-BACA-BA408E06B297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902CB03F-2D02-4F16-A0E4-CD788D616C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>CN</t>
@@ -4240,13 +4244,13 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4277,7 +4281,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4324,10 +4328,10 @@
         <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4421,7 +4425,7 @@
         <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4429,7 +4433,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4442,7 +4446,7 @@
         <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4450,7 +4454,7 @@
         <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -6627,7 +6631,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12798,7 +12802,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19821,4 +19825,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902CB03F-2D02-4F16-A0E4-CD788D616C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E960AD-3133-43B4-A36A-FF8DD22B2F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2504,7 +2517,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2944,6 +2957,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3147,11 +3166,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3936,9 +3956,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{25FD31BA-A39D-4BF9-8DAD-C9131254E400}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4023,6 +4049,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>4421354800</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>5.53</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>10000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19828,22 +19937,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78217F3E-66CB-40DF-B4DC-8D353C98A481}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E960AD-3133-43B4-A36A-FF8DD22B2F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F40D36C-73F1-4BF9-998B-2185549F9873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3920,47 +3920,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4449,7 +4449,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>5.53</v>
+        <v>5.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24450.092044000001</v>
+        <v>24715.373331999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4507,13 +4507,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4589,14 +4589,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>6.9895661568976033</v>
+        <v>6.1203199055974453</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11156651152863062</v>
+        <v>6.2099536522534526E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>3.1476386351257846</v>
+        <v>2.2777045899700505</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4638,7 +4638,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>3.931774672331573</v>
+        <v>3.1142971805177257</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4657,7 +4657,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>6.3521223870188166</v>
+        <v>5.3970513031335168</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4676,7 +4676,7 @@
         <v>433</v>
       </c>
       <c r="F31" s="312">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>5.902408832447132</v>
+        <v>5.225618425612172</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4713,13 +4713,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4740,13 +4740,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4766,13 +4766,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4801,13 +4801,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4823,13 +4823,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4893,13 +4893,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4915,13 +4915,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4937,22 +4937,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.1591337580733148E-2</v>
+        <v>4.114491893049272E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.2712477396021691E-2</v>
+        <v>3.2361359570661892E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -5087,13 +5087,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5146,22 +5146,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.8333349470242393</v>
+        <v>3.0666679576193911</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5198,13 +5198,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5217,13 +5217,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5345,13 +5345,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>6.2281210528207165</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5390,13 +5390,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>8.85 CNY</v>
+        <v>7.7 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>7.26 CNY</v>
+        <v>6.36 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>6.83 CNY</v>
+        <v>5.98 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>6.34 CNY</v>
+        <v>5.56 CNY</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>6.23 CNY</v>
+        <v>5.46 CNY</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>6.9895661568976033</v>
+        <v>6.1203199055974453</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5539,13 +5539,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5558,22 +5558,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.3067846364883402</v>
+        <v>0.27013727500102497</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>2.8408539986374444</v>
+        <v>2.0075673149690254</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>3.1476386351257846</v>
+        <v>2.2777045899700505</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54966609307795733</v>
+        <v>0.62784550070872336</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.35311679999999995</v>
+        <v>0.32853482020937647</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>3.578657872331573</v>
+        <v>2.7857623603083495</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>3.931774672331573</v>
+        <v>3.1142971805177257</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43747943948544943</v>
+        <v>0.49115451013116307</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.4835478616576106</v>
+        <v>0.47043510634283742</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>5.8685745253612058</v>
+        <v>4.926616196790679</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>6.3521223870188166</v>
+        <v>5.3970513031335168</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>9.119933277256842E-2</v>
+        <v>0.11817496693309293</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>5.4420382208736449</v>
+        <v>4.7652478140386849</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>5.902408832447132</v>
+        <v>5.225618425612172</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.1547224233415424</v>
+        <v>0.14605011159067327</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5906,13 +5906,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5920,13 +5920,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5949,13 +5949,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5963,22 +5963,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6002,6 +6002,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6018,17 +6029,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13615,16 +13615,16 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2712477396021691E-2</v>
+        <v>3.2361359570661892E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2712477396021691E-2</v>
+        <v>3.2361359570661892E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.3924050632911392E-2</v>
+        <v>2.3667262969588553E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
@@ -14814,50 +14814,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1591337580733148E-2</v>
+        <v>4.114491893049272E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.839669088310645E-2</v>
+        <v>5.7769892769870962E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5361062359100266E-2</v>
+        <v>5.476684702071994E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>3.1327248731559412E-2</v>
+        <v>3.0990999192401354E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.4831524828023512E-2</v>
+        <v>2.4564996833447234E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>1.1443338678332689E-2</v>
+        <v>1.1320512145112661E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>1.595968028453763E-2</v>
+        <v>1.5788377812789463E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>-3.3237905836117697E-3</v>
+        <v>-3.2881148349504629E-3</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>4.1348357387803382E-2</v>
+        <v>4.0904546753945024E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2137190854985857E-2</v>
+        <v>2.189958236638136E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11974482851562385</v>
+        <v>0.1184595530753846</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14871,43 +14871,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9418612251666821E-2</v>
+        <v>8.8458841816049655E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6680264314182058E-2</v>
+        <v>6.5964554858215882E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9291793151173465E-2</v>
+        <v>5.8655387500176966E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.52143762620839E-2</v>
+        <v>1.5051073475728795E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4950098115876033E-2</v>
+        <v>1.478963194647486E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1716215198064961E-3</v>
+        <v>1.1590459757656393E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2653813268401291E-3</v>
+        <v>3.2303325111674264E-3</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.002577994875707E-2</v>
+        <v>1.9810834189020861E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3697605090291901E-2</v>
+        <v>5.3121244391648344E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13947880804959475</v>
+        <v>0.13798171887553828</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15689,16 +15689,16 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1694853.3868033364</v>
+        <v>1355882.7094426691</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15713,8 +15713,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15729,8 +15729,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15745,8 +15745,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15755,7 +15755,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>2753673.291186993</v>
+        <v>2414702.6138263256</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>6.2281210528207165</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15836,7 +15836,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.9828054066931156</v>
+        <v>6.1193502060712941</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15879,11 +15879,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>101820.79011492425</v>
+        <v>100400.03490401834</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15901,11 +15901,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>101950.54215654559</v>
+        <v>99125.260501542143</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15923,11 +15923,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>102080.45954349852</v>
+        <v>97866.671848192069</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15955,11 +15955,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>102210.54248648556</v>
+        <v>96624.063434291806</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15987,11 +15987,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>102340.79119647763</v>
+        <v>95397.23235951153</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16019,11 +16019,11 @@
       </c>
       <c r="E26" s="124">
         <f t="shared" si="0"/>
-        <v>0.70496054043967626</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>102471.20588471467</v>
+        <v>94185.978299737195</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16041,11 +16041,11 @@
       </c>
       <c r="E27" s="124">
         <f t="shared" si="0"/>
-        <v>0.66505711362233599</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>102601.78676270564</v>
+        <v>92990.103474360236</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16063,11 +16063,11 @@
       </c>
       <c r="E28" s="124">
         <f t="shared" si="0"/>
-        <v>0.62741237134182648</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>102732.53404222913</v>
+        <v>91809.412613983019</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16085,11 +16085,11 @@
       </c>
       <c r="E29" s="124">
         <f t="shared" si="0"/>
-        <v>0.59189846353002495</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>102863.44793533355</v>
+        <v>90643.712928534034</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16107,11 +16107,11 @@
       </c>
       <c r="E30" s="124">
         <f t="shared" si="0"/>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>102994.52865433756</v>
+        <v>89492.814075788032</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1798833.9586969954</v>
+        <v>1439067.1669575963</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16639,11 +16639,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>1004459.4870739471</v>
+        <v>698226.65182581544</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16654,7 +16654,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>2028526.1158511993</v>
+        <v>1646761.9362657736</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16675,7 +16675,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>2028526.1158511993</v>
+        <v>1646761.9362657736</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16705,19 +16705,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1694853.386803336</v>
+        <v>1355882.7094426691</v>
       </c>
       <c r="C56" s="123">
-        <v>1720030.814793431</v>
+        <v>1377227.3778092652</v>
       </c>
       <c r="D56" s="123">
-        <v>1824063.1825040856</v>
+        <v>1465737.6878832947</v>
       </c>
       <c r="E56" s="123">
-        <v>1905783.395825529</v>
+        <v>1535602.8534480981</v>
       </c>
       <c r="F56" s="123">
-        <v>1962138.7895844979</v>
+        <v>1583946.0012884834</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16726,19 +16726,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>1694853.3868033355</v>
+        <v>1355882.7094426695</v>
       </c>
       <c r="C57" s="123">
-        <v>1742984.9715916547</v>
+        <v>1397692.2561812825</v>
       </c>
       <c r="D57" s="123">
-        <v>1959330.3932692662</v>
+        <v>1586267.2610946798</v>
       </c>
       <c r="E57" s="123">
-        <v>2150754.4939556615</v>
+        <v>1753787.7887244106</v>
       </c>
       <c r="F57" s="123">
-        <v>2294801.7487464733</v>
+        <v>1880145.645094349</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16747,19 +16747,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>1694853.386803335</v>
+        <v>1355882.7094426693</v>
       </c>
       <c r="C58" s="341">
-        <v>1773335.93203612</v>
+        <v>1422959.0385313975</v>
       </c>
       <c r="D58" s="123">
-        <v>2157725.5203181584</v>
+        <v>1751328.6343555111</v>
       </c>
       <c r="E58" s="123">
-        <v>2540966.1638217429</v>
+        <v>2078278.3794548714</v>
       </c>
       <c r="F58" s="123">
-        <v>2855784.043374842</v>
+        <v>2346486.2856683689</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16778,19 +16778,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>1694853.3868033355</v>
+        <v>1355882.7094426695</v>
       </c>
       <c r="C59" s="341">
-        <v>1806381.5450048302</v>
+        <v>1448620.4599971627</v>
       </c>
       <c r="D59" s="123">
-        <v>2398788.937638829</v>
+        <v>1938406.7120858128</v>
       </c>
       <c r="E59" s="123">
-        <v>3060004.4790359829</v>
+        <v>2480866.4929666566</v>
       </c>
       <c r="F59" s="123">
-        <v>3650942.2694116104</v>
+        <v>2963014.3767434643</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16809,19 +16809,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>1694853.3868033353</v>
+        <v>1355882.7094426695</v>
       </c>
       <c r="C60" s="341">
-        <v>1839216.0489163534</v>
+        <v>1472396.9814872369</v>
       </c>
       <c r="D60" s="123">
-        <v>2667440.5303773354</v>
+        <v>2132817.6215176256</v>
       </c>
       <c r="E60" s="123">
-        <v>3697592.1928683338</v>
+        <v>2941998.5631594639</v>
       </c>
       <c r="F60" s="123">
-        <v>4697585.6601613443</v>
+        <v>3719689.4933723528</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16840,19 +16840,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>1694853.386803335</v>
+        <v>1355882.7094426693</v>
       </c>
       <c r="C61" s="341">
-        <v>1870145.566212385</v>
+        <v>1493279.3992441394</v>
       </c>
       <c r="D61" s="123">
-        <v>2952610.4159092563</v>
+        <v>2325221.4882031037</v>
       </c>
       <c r="E61" s="123">
-        <v>4448232.5208333777</v>
+        <v>3448151.6681637811</v>
       </c>
       <c r="F61" s="123">
-        <v>6024212.9296894623</v>
+        <v>4613846.2892309753</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16932,23 +16932,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>6.2281210528207165</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>6.2281210528207165</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>6.2281210528207165</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>6.2281210528207165</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>6.2281210528207165</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16959,23 +16959,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.2281210528207165</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>6.2850661050252912</v>
+        <v>5.5097303708648804</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.520361331073774</v>
+        <v>5.7099185803115171</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.7051920379906749</v>
+        <v>5.8679361308704623</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>6.8326538597810664</v>
+        <v>5.9772762540390101</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16986,23 +16986,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>6.2281210528207147</v>
+        <v>5.4614540634158697</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>6.3369826732188761</v>
+        <v>5.5560168131382239</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>6.8263019689189441</v>
+        <v>5.9825263638157606</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>7.259255462464397</v>
+        <v>6.3614159467773694</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>7.585054366435668</v>
+        <v>6.647205850745129</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17013,23 +17013,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>6.2281210528207138</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>6.4056289633661088</v>
+        <v>5.6131639625823606</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>7.2750221825713135</v>
+        <v>6.3558539539490653</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>8.141816775720871</v>
+        <v>7.0953325976882198</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>8.8538561704174903</v>
+        <v>7.7019518769496296</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17040,23 +17040,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>6.2281210528207147</v>
+        <v>5.4614540634158697</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>6.4803698843361017</v>
+        <v>5.6712036871160381</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>7.8202474092838816</v>
+        <v>6.7789778293057799</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>9.3157517768527409</v>
+        <v>8.0058863345468527</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>10.652305428633023</v>
+        <v>9.0963843958578501</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17067,23 +17067,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>6.2281210528207138</v>
+        <v>5.4614540634158697</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>6.5546333293587073</v>
+        <v>5.7249802387967001</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>8.4278701966216136</v>
+        <v>7.2186867380588469</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>10.757815901252689</v>
+        <v>9.0488518757714722</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>13.019551302566807</v>
+        <v>10.80779447457148</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17093,23 +17093,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>6.2281210528207138</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>6.6245881705671783</v>
+        <v>5.7722110508475728</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>9.0728532356030627</v>
+        <v>7.6538562175258145</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>12.455576795639731</v>
+        <v>10.193643750434681</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>16.020050763791041</v>
+        <v>12.830153765571206</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>8.8538561704174903</v>
+        <v>7.7019518769496296</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>7.259255462464397</v>
+        <v>6.3614159467773694</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>6.8263019689189441</v>
+        <v>5.9825263638157606</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>6.3369826732188761</v>
+        <v>5.5560168131382239</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17235,7 +17235,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>6.2281210528207138</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17438,7 +17438,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17449,14 +17449,14 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1333038.4722</v>
+        <v>1066430.77776</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17465,7 +17465,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>3.0150000000000001</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>3.6085754006290576</v>
+        <v>2.9294494004615776</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17561,11 +17561,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>80084.231208339406</v>
+        <v>78966.776819385836</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17583,11 +17583,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>80186.283966810734</v>
+        <v>77964.139461424376</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17605,11 +17605,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>80288.466772925065</v>
+        <v>76974.232541655671</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17627,11 +17627,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>80390.779792404443</v>
+        <v>75996.894422319761</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17649,11 +17649,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>80493.223191182056</v>
+        <v>75031.965517963545</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17671,11 +17671,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" si="0"/>
-        <v>0.70496054043967626</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>80595.797135402579</v>
+        <v>74079.288269382771</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -17693,11 +17693,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.66505711362233599</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>80698.501791422357</v>
+        <v>73138.707117894679</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -17715,11 +17715,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.62741237134182648</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>80801.337325809815</v>
+        <v>72210.068479937734</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -17737,11 +17737,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.59189846353002495</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>80904.303905345543</v>
+        <v>71293.22072199345</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -17759,11 +17759,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>81007.401697022695</v>
+        <v>70388.014135826772</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18213,7 +18213,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>1414821.4180139964</v>
+        <v>1131857.1344111972</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18221,11 +18221,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>790028.8900866562</v>
+        <v>549170.20932100737</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>1595479.2168733208</v>
+        <v>1295213.516808792</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18257,7 +18257,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>1595479.2168733208</v>
+        <v>1295213.516808792</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18287,19 +18287,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>1333038.4721999995</v>
+        <v>1066430.7777600002</v>
       </c>
       <c r="C51" s="123">
-        <v>1352841.0583134475</v>
+        <v>1083218.8163777171</v>
       </c>
       <c r="D51" s="123">
-        <v>1434664.7426463575</v>
+        <v>1152834.0700826817</v>
       </c>
       <c r="E51" s="123">
-        <v>1498939.4398927903</v>
+        <v>1207784.5184752494</v>
       </c>
       <c r="F51" s="123">
-        <v>1543264.1635424129</v>
+        <v>1245807.4391834722</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18308,19 +18308,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>1333038.4721999993</v>
+        <v>1066430.7777600002</v>
       </c>
       <c r="C52" s="123">
-        <v>1370894.9940386233</v>
+        <v>1099314.8813301236</v>
       </c>
       <c r="D52" s="123">
-        <v>1541055.2997182389</v>
+        <v>1247633.1597146548</v>
       </c>
       <c r="E52" s="123">
-        <v>1691614.4529217728</v>
+        <v>1379391.6409806137</v>
       </c>
       <c r="F52" s="123">
-        <v>1804910.7025832951</v>
+        <v>1478774.8000888736</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18329,19 +18329,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>1333038.472199999</v>
+        <v>1066430.77776</v>
       </c>
       <c r="C53" s="123">
-        <v>1394766.6741825927</v>
+        <v>1119187.7465606285</v>
       </c>
       <c r="D53" s="123">
-        <v>1697097.314391847</v>
+        <v>1377457.4634238132</v>
       </c>
       <c r="E53" s="123">
-        <v>1998524.2849361985</v>
+        <v>1634610.437295767</v>
       </c>
       <c r="F53" s="123">
-        <v>2246135.2868366255</v>
+        <v>1845561.6973366968</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18350,19 +18350,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>1333038.4721999993</v>
+        <v>1066430.7777600002</v>
       </c>
       <c r="C54" s="123">
-        <v>1420757.756224094</v>
+        <v>1139371.0039040397</v>
       </c>
       <c r="D54" s="123">
-        <v>1886698.8528084233</v>
+        <v>1524598.3765325719</v>
       </c>
       <c r="E54" s="123">
-        <v>2406759.0314421728</v>
+        <v>1951254.6071928665</v>
       </c>
       <c r="F54" s="123">
-        <v>2871544.2543889983</v>
+        <v>2330474.2396216849</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18371,19 +18371,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>1333038.472199999</v>
+        <v>1066430.7777600002</v>
       </c>
       <c r="C55" s="123">
-        <v>1446582.7964726875</v>
+        <v>1158071.7470645669</v>
       </c>
       <c r="D55" s="123">
-        <v>2097999.0817997293</v>
+        <v>1677506.7187560801</v>
       </c>
       <c r="E55" s="123">
-        <v>2908235.4178708652</v>
+        <v>2313944.8523306139</v>
       </c>
       <c r="F55" s="123">
-        <v>3694751.6877911109</v>
+        <v>2925615.4177770391</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18392,19 +18392,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>1333038.4721999988</v>
+        <v>1066430.7777600002</v>
       </c>
       <c r="C56" s="123">
-        <v>1470909.523966179</v>
+        <v>1174496.2156818833</v>
       </c>
       <c r="D56" s="123">
-        <v>2322291.3016972309</v>
+        <v>1828836.4788927562</v>
       </c>
       <c r="E56" s="123">
-        <v>3498630.1055491441</v>
+        <v>2712045.1051594634</v>
       </c>
       <c r="F56" s="123">
-        <v>4738172.4357568584</v>
+        <v>3628888.8798590619</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18454,23 +18454,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>3.0150000000000001</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>3.0150000000000001</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>3.0150000000000001</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>3.0150000000000001</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>3.0150000000000001</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18481,23 +18481,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>3.0149999999999992</v>
+        <v>2.4120000000000004</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>3.0597885026405196</v>
+        <v>2.4499703493094853</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>3.2448532351358854</v>
+        <v>2.6074226616752894</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>3.3902265429881138</v>
+        <v>2.7317068480350173</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>3.4904779945332884</v>
+        <v>2.8177051956641712</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18508,23 +18508,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>3.0149999999999983</v>
+        <v>2.4120000000000004</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>3.1006219949564402</v>
+        <v>2.486375627059207</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>3.4854820963887332</v>
+        <v>2.8218345193981147</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>3.8260092877454053</v>
+        <v>3.1198392876785501</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>4.0822571004328703</v>
+        <v>3.3446191653492128</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18535,23 +18535,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>3.0149999999999979</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>3.1546137717393608</v>
+        <v>2.5313230835051477</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>3.8384101506439769</v>
+        <v>3.1154646612477546</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>4.5201626545243521</v>
+        <v>3.6970804453326549</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0801968818169163</v>
+        <v>4.174199494997997</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18562,23 +18562,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>3.0149999999999983</v>
+        <v>2.4120000000000004</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>3.2133991061384486</v>
+        <v>2.5769725693672894</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>4.2672414636536828</v>
+        <v>3.4482606474661832</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>5.4434876645551551</v>
+        <v>4.4132504525374587</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.4947157246665617</v>
+        <v>5.2709505231782909</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18589,23 +18589,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>3.0149999999999979</v>
+        <v>2.4120000000000004</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>3.2718088954830935</v>
+        <v>2.6192689785143841</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>4.7451497939041882</v>
+        <v>3.7941011175038026</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.57770197015373</v>
+        <v>5.2335651785525421</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>8.356605282595984</v>
+        <v>6.6170111880119622</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18615,23 +18615,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>3.0149999999999975</v>
+        <v>2.4120000000000004</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>3.3268298756891865</v>
+        <v>2.6564170233112332</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>5.2524427618820164</v>
+        <v>4.136371229227648</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>7.9130272593123356</v>
+        <v>6.1339684957186957</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>10.716562343643758</v>
+        <v>8.2076400651199997</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.0801968818169163</v>
+        <v>4.174199494997997</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18688,7 +18688,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>3.8260092877454053</v>
+        <v>3.1198392876785501</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>3.4854820963887332</v>
+        <v>2.8218345193981147</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>3.1006219949564402</v>
+        <v>2.486375627059207</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>3.0149999999999979</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-5.53</v>
+        <v>-5.59</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>7.1704661568976036</v>
+        <v>6.3012199055974456</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18921,11 +18921,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 海油工程(600583.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18946,8 +18946,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18968,8 +18968,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18979,8 +18979,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18993,8 +18993,8 @@
       <c r="B11" s="159" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19012,8 +19012,8 @@
         <v>0.14806091180696912</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19030,8 +19030,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.32719702788845018</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19048,8 +19048,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.32982639766138688</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19075,21 +19075,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19097,14 +19097,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>5.53</v>
+        <v>5.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19112,14 +19112,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>6.2281210528207165</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19139,8 +19139,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19150,8 +19150,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19159,14 +19159,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>6.8263019689189441</v>
+        <v>5.9825263638157606</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19176,8 +19176,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19197,8 +19197,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19208,8 +19208,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19217,14 +19217,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>6.3369826732188761</v>
+        <v>5.5560168131382239</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19234,8 +19234,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19255,8 +19255,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19266,8 +19266,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19275,14 +19275,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>7.259255462464397</v>
+        <v>6.3614159467773694</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -19293,8 +19293,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>6.8150288084880213</v>
+        <v>5.9730023702725754</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19356,8 +19356,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="370"/>
+      <c r="F49" s="370"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19367,8 +19367,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19376,14 +19376,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>6.2281210528207138</v>
+        <v>5.4614540634158688</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="370"/>
+      <c r="F51" s="370"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19393,8 +19393,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="370"/>
+      <c r="F52" s="370"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19414,8 +19414,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="370"/>
+      <c r="F55" s="370"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19425,8 +19425,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="370"/>
+      <c r="F56" s="370"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19434,14 +19434,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>8.8538561704174903</v>
+        <v>7.7019518769496296</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="370"/>
+      <c r="F57" s="370"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19451,8 +19451,8 @@
         <v>0.1</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>6.9895661568976033</v>
+        <v>6.1203199055974453</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19522,7 +19522,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>6.9828054066931156</v>
+        <v>6.1193502060712941</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.34262299719893202</v>
+        <v>0.39128446596497091</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19636,7 +19636,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19645,7 +19645,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.3067846364883402</v>
+        <v>0.27013727500102497</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19657,7 +19657,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>2.8408539986374444</v>
+        <v>2.0075673149690254</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>3.1476386351257846</v>
+        <v>2.2777045899700505</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.54966609307795733</v>
+        <v>0.62784550070872336</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>5.53</v>
+        <v>5.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11156651152863062</v>
+        <v>6.2099536522534526E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.35311679999999995</v>
+        <v>0.32853482020937647</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>3.578657872331573</v>
+        <v>2.7857623603083495</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>3.931774672331573</v>
+        <v>3.1142971805177257</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43747943948544943</v>
+        <v>0.49115451013116307</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.4835478616576106</v>
+        <v>0.47043510634283742</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19806,7 +19806,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>5.8685745253612058</v>
+        <v>4.926616196790679</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19818,7 +19818,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>6.3521223870188166</v>
+        <v>5.3970513031335168</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19828,7 +19828,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>9.119933277256842E-2</v>
+        <v>0.11817496693309293</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>5.4420382208736449</v>
+        <v>4.7652478140386849</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>5.902408832447132</v>
+        <v>5.225618425612172</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.1547224233415424</v>
+        <v>0.14605011159067327</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19941,19 +19941,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="372"/>
+    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="360"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="370" t="s">
+      <c r="B2" s="358" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/600583.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600583.SS_Valuation.xlsx
@@ -8,45 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F40D36C-73F1-4BF9-998B-2185549F9873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D0438A-9AF7-4C5B-A68D-7D84A8F96C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="DDM" sheetId="10" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId3"/>
+    <sheet name="BS" sheetId="3" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId7"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
-    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,20 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="561">
   <si>
     <t>Sales</t>
   </si>
@@ -411,10 +406,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1348,10 +1339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1504,10 +1491,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1525,10 +1508,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1760,71 +1739,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1864,32 +1783,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1987,30 +1880,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2034,58 +1903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2103,23 +1920,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2162,10 +1962,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2284,10 +2080,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2334,133 +2126,1148 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
   <si>
     <t>CN</t>
@@ -3171,7 +3978,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3920,33 +4727,55 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3961,10 +4790,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{25FD31BA-A39D-4BF9-8DAD-C9131254E400}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{3256A913-21DB-4867-9632-97B0F8432CDD}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4076,7 +4910,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>5.53</v>
+            <v>5.59</v>
           </cell>
         </row>
         <row r="13">
@@ -4101,7 +4935,7 @@
         </row>
         <row r="86">
           <cell r="C86">
-            <v>0.06</v>
+            <v>7.4999999999999997E-2</v>
           </cell>
         </row>
         <row r="92">
@@ -4331,6 +5165,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45797</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>CN</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>海油工程</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>4421354800</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>600583.SS</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>5.59</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>24715.373331999999</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>ENG_03</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (CNY) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>6.1203199055974453</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>6.2099536522534526E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>600583.SS (CNY)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>2.2777045899700505</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>3.1142971805177257</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>5.3970513031335168</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>5.225618425612172</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>135997.4245838768</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>154945.9</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>-154945.9</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>4618.7267156970447</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-1984.19</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>2634.5367156970447</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-2282.7677664801586</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-34657.990324893457</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>142780.44671569683</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>101691.20320820018</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>4.114491893049272E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>3.2361359570661892E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>0.87391267559349473</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>4.9029562887232557E-2</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>6.8755155989910458E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>5.0475725130946753E-2</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>6.490075699179193E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.56944999111533989</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.62106298336522048</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.7057676125178334</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.7057676125178334</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>3.0666679576193911</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>72651.94</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.16432053813007724</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>2.5694600492681609E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>0.53421555755411909</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>606704.22</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>381755.93838365644</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.86343656108226474</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>749715.90599999996</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.6956700828442901</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>5.4614540634158688</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>-0.36074239393771346</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.1</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>15</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>7.7 CNY</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.08</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>10</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>6.36 CNY</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.05</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>10</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>5.98 CNY</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.01</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>10</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>5.56 CNY</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>15</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>5.46 CNY</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>6.1203199055974453</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.18089999999999998</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>600583.SS</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>0.27013727500102497</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>2.0075673149690254</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>2.2777045899700505</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.62784550070872336</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>0.32853482020937647</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>2.7857623603083495</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>3.1142971805177257</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.49115451013116307</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>0.47043510634283742</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>4.926616196790679</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>5.3970513031335168</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>0.11817496693309293</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>0.46037061157348735</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>4.7652478140386849</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>5.225618425612172</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.14605011159067327</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4347,24 +6924,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4378,7 +6955,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4387,15 +6964,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C6" s="51">
         <v>4421354800</v>
@@ -4404,7 +6981,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4414,7 +6991,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4427,26 +7004,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="C12" s="50">
         <v>5.59</v>
@@ -4456,17 +7033,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4480,7 +7057,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4494,7 +7071,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="C16" s="50">